--- a/WeiJingShuZhi/属性表.xlsx
+++ b/WeiJingShuZhi/属性表.xlsx
@@ -1,45 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitMengJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC6D93F-9011-4A22-957D-781B94F16DD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E4BC27F-E0BD-4028-8EC9-B3954D75D477}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
-    <sheet name="等级属性" sheetId="2" r:id="rId2"/>
-    <sheet name="活力属性" sheetId="3" r:id="rId3"/>
-    <sheet name="技能" sheetId="4" r:id="rId4"/>
-    <sheet name="赛季" sheetId="5" r:id="rId5"/>
-    <sheet name="装备洗练" sheetId="6" r:id="rId6"/>
-    <sheet name="装备属性" sheetId="7" r:id="rId7"/>
-    <sheet name="特殊装备" sheetId="8" r:id="rId8"/>
-    <sheet name="觉醒" sheetId="9" r:id="rId9"/>
-    <sheet name="增幅属性" sheetId="10" r:id="rId10"/>
-    <sheet name="收集" sheetId="11" r:id="rId11"/>
-    <sheet name="精灵" sheetId="12" r:id="rId12"/>
-    <sheet name="属性列表" sheetId="13" r:id="rId13"/>
-    <sheet name="宝石" sheetId="14" r:id="rId14"/>
-    <sheet name="宠物" sheetId="15" r:id="rId15"/>
-    <sheet name="宠物属性" sheetId="16" r:id="rId16"/>
-    <sheet name="宠物爬塔" sheetId="17" r:id="rId17"/>
-    <sheet name="宠物之核" sheetId="18" r:id="rId18"/>
-    <sheet name="装备" sheetId="19" r:id="rId19"/>
-    <sheet name="怪物属性" sheetId="20" r:id="rId20"/>
-    <sheet name="boss技能" sheetId="21" r:id="rId21"/>
-    <sheet name="称号" sheetId="22" r:id="rId22"/>
-    <sheet name="生命之盾" sheetId="23" r:id="rId23"/>
+    <sheet name="属性介绍" sheetId="24" r:id="rId2"/>
+    <sheet name="等级属性" sheetId="2" r:id="rId3"/>
+    <sheet name="活力属性" sheetId="3" r:id="rId4"/>
+    <sheet name="技能" sheetId="4" r:id="rId5"/>
+    <sheet name="赛季" sheetId="5" r:id="rId6"/>
+    <sheet name="装备洗练" sheetId="6" r:id="rId7"/>
+    <sheet name="装备属性" sheetId="7" r:id="rId8"/>
+    <sheet name="特殊装备" sheetId="8" r:id="rId9"/>
+    <sheet name="觉醒" sheetId="9" r:id="rId10"/>
+    <sheet name="增幅属性" sheetId="10" r:id="rId11"/>
+    <sheet name="收集" sheetId="11" r:id="rId12"/>
+    <sheet name="精灵" sheetId="12" r:id="rId13"/>
+    <sheet name="属性列表" sheetId="13" r:id="rId14"/>
+    <sheet name="宝石" sheetId="14" r:id="rId15"/>
+    <sheet name="宠物" sheetId="15" r:id="rId16"/>
+    <sheet name="宠物属性" sheetId="16" r:id="rId17"/>
+    <sheet name="宠物爬塔" sheetId="17" r:id="rId18"/>
+    <sheet name="宠物之核" sheetId="18" r:id="rId19"/>
+    <sheet name="装备" sheetId="19" r:id="rId20"/>
+    <sheet name="怪物属性" sheetId="20" r:id="rId21"/>
+    <sheet name="boss技能" sheetId="21" r:id="rId22"/>
+    <sheet name="称号" sheetId="22" r:id="rId23"/>
+    <sheet name="生命之盾" sheetId="23" r:id="rId24"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
   <calcPr calcId="191029"/>
 </workbook>
@@ -89,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5225" uniqueCount="2956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5421" uniqueCount="3089">
   <si>
     <t>人物属性</t>
   </si>
@@ -9289,6 +9290,522 @@
     <t>系数</t>
     <phoneticPr fontId="35" type="noConversion"/>
   </si>
+  <si>
+    <t>属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色能够承受的伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>防御力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高普通攻击和技能基础伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少受到的物理伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>法术强度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击速度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高普通攻击频率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击强度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高近战普通攻击的效果</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高魔法技能的伤害效果</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>移动速度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高角色移动速度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击产生暴击的概率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>百分比</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击时造成的额外伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低攻击落空概率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>有概率完全躲避攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗暴率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>抵抗暴击的概率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>火系伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>水系伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗系伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>光系伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>可以</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每个技能有对应的系列,对应系列的技能伤害提升</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>冷却缩减</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少技能冷却时间</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>金币加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高获得的金币</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高获得的经验</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>火系抗性</t>
+  </si>
+  <si>
+    <t>每个技能有对应的系列,对应系列的技能抗性提升</t>
+  </si>
+  <si>
+    <t>水系抗性</t>
+  </si>
+  <si>
+    <t>暗系抗性</t>
+  </si>
+  <si>
+    <t>光系抗性</t>
+  </si>
+  <si>
+    <t>自然抗性</t>
+  </si>
+  <si>
+    <t>降低敌人防御力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>穿透</t>
+  </si>
+  <si>
+    <t>斩击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>当目标血量低于30%,额外造成的伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>集中</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离敌人越远，伤害越高</t>
+  </si>
+  <si>
+    <t>对目标持续3秒后输出变高</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>距离敌人越近，伤害越高</t>
+  </si>
+  <si>
+    <t>距离增伤</t>
+  </si>
+  <si>
+    <t>贴身增伤</t>
+  </si>
+  <si>
+    <t>溅射</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>对有主目标的普通攻击和技能攻击的伤害可以扩散到附近的单位</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常状态</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>灼烧</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>持续造成火焰伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>固定值,秒</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
+    <t>无法释放技能</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>缴械</t>
+  </si>
+  <si>
+    <t>无法攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>恐惧</t>
+  </si>
+  <si>
+    <t>让敌人四处游走</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>效果描述</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>无法移动和释放技能和攻击</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>格挡</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能抵抗</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到技能将会减免一定的伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>有一定概率抵抗普通攻击造成的伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常抗性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>降低负面状态命中概率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害减免</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>造成伤害的总加成</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害的总减免</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>首领减伤</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>减少Boss造成的伤害</t>
+  </si>
+  <si>
+    <t>首领增伤</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加Boss造成的伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能属性类型</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>火系</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>水系</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暗系</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>光系</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>电系</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>电系抗性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>电系伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗增效</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复药剂的生命以及恢复类技能的恢复量提高</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>免费施法</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能有概率不进入冷却时间</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>感电：受到攻击时有概率将此伤害向附近敌人传导伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>传到一个人有电击的效果,逐个的传递</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>侵蚀：降低防御和受到的治疗效果</t>
+  </si>
+  <si>
+    <t>圣痕：目标受到的伤害提高</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>灼烧：持续受到伤害；叠满后触发爆燃</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>潮湿：降低移动速度，并强化电系效果</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>中毒：持续伤害,并降低移动速度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>表现效果参考</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>一类属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>力量</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>智力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏捷</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>体质</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高生命值</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>耐力</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高防御属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>眩晕恢复</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到眩晕冷却降低多少</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高攻击强度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>提高法术强度</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加攻击属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加普攻伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加所有技能类伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>每次攻击概率忽略目标的抗性或护甲</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>反弹伤害</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到伤害有一定概率将此伤害反弹给目标敌人</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>增加自身的技能抵抗概率和格挡的概率</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果当前属性比玩家属性高</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>对比属性</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>暴击提升5%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>闪避提升5%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>命中提升5%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>抗暴提升5%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
+  <si>
+    <t>技能伤害提升5%</t>
+    <phoneticPr fontId="35" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -9297,7 +9814,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="38">
+  <fonts count="39">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -9567,6 +10084,15 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="21">
     <fill>
@@ -9800,7 +10326,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -10131,6 +10657,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -14125,44 +14657,44 @@
     <row r="30" spans="10:15" ht="20.100000000000001" customHeight="1"/>
     <row r="31" spans="10:15" ht="20.100000000000001" customHeight="1"/>
     <row r="32" spans="10:15" ht="20.100000000000001" customHeight="1"/>
-    <row r="33" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="35" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="36" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="37" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="38" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="39" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="40" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="41" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="42" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="43" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="44" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="45" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="46" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="47" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="48" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="49" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="50" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="51" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="52" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="53" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="54" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="55" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="56" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="57" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="58" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="59" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="60" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="61" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="62" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="63" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="64" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="65" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="66" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="67" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="68" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="69" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
-    <row r="70" s="98" customFormat="1" ht="20.100000000000001" customHeight="1"/>
+    <row r="33" ht="20.100000000000001" customHeight="1"/>
+    <row r="34" ht="20.100000000000001" customHeight="1"/>
+    <row r="35" ht="20.100000000000001" customHeight="1"/>
+    <row r="36" ht="20.100000000000001" customHeight="1"/>
+    <row r="37" ht="20.100000000000001" customHeight="1"/>
+    <row r="38" ht="20.100000000000001" customHeight="1"/>
+    <row r="39" ht="20.100000000000001" customHeight="1"/>
+    <row r="40" ht="20.100000000000001" customHeight="1"/>
+    <row r="41" ht="20.100000000000001" customHeight="1"/>
+    <row r="42" ht="20.100000000000001" customHeight="1"/>
+    <row r="43" ht="20.100000000000001" customHeight="1"/>
+    <row r="44" ht="20.100000000000001" customHeight="1"/>
+    <row r="45" ht="20.100000000000001" customHeight="1"/>
+    <row r="46" ht="20.100000000000001" customHeight="1"/>
+    <row r="47" ht="20.100000000000001" customHeight="1"/>
+    <row r="48" ht="20.100000000000001" customHeight="1"/>
+    <row r="49" ht="20.100000000000001" customHeight="1"/>
+    <row r="50" ht="20.100000000000001" customHeight="1"/>
+    <row r="51" ht="20.100000000000001" customHeight="1"/>
+    <row r="52" ht="20.100000000000001" customHeight="1"/>
+    <row r="53" ht="20.100000000000001" customHeight="1"/>
+    <row r="54" ht="20.100000000000001" customHeight="1"/>
+    <row r="55" ht="20.100000000000001" customHeight="1"/>
+    <row r="56" ht="20.100000000000001" customHeight="1"/>
+    <row r="57" ht="20.100000000000001" customHeight="1"/>
+    <row r="58" ht="20.100000000000001" customHeight="1"/>
+    <row r="59" ht="20.100000000000001" customHeight="1"/>
+    <row r="60" ht="20.100000000000001" customHeight="1"/>
+    <row r="61" ht="20.100000000000001" customHeight="1"/>
+    <row r="62" ht="20.100000000000001" customHeight="1"/>
+    <row r="63" ht="20.100000000000001" customHeight="1"/>
+    <row r="64" ht="20.100000000000001" customHeight="1"/>
+    <row r="65" ht="20.100000000000001" customHeight="1"/>
+    <row r="66" ht="20.100000000000001" customHeight="1"/>
+    <row r="67" ht="20.100000000000001" customHeight="1"/>
+    <row r="68" ht="20.100000000000001" customHeight="1"/>
+    <row r="69" ht="20.100000000000001" customHeight="1"/>
+    <row r="70" ht="20.100000000000001" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14170,6 +14702,582 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:R41"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="9" max="9" width="11.75" customWidth="1"/>
+    <col min="10" max="10" width="36.5" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="21.625" customWidth="1"/>
+    <col min="14" max="14" width="9" style="36"/>
+    <col min="16" max="16" width="23.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N1" s="38"/>
+    </row>
+    <row r="2" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I2" s="1" t="s">
+        <v>1506</v>
+      </c>
+      <c r="N2" s="38"/>
+    </row>
+    <row r="3" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="H3" s="1" t="s">
+        <v>1507</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1508</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>1509</v>
+      </c>
+      <c r="N3" s="38"/>
+    </row>
+    <row r="4" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I4" s="1">
+        <v>2</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>1510</v>
+      </c>
+      <c r="N4" s="38"/>
+    </row>
+    <row r="5" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I5" s="1">
+        <v>3</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>1511</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="N5" s="38"/>
+      <c r="P5" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>1513</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I6" s="1">
+        <v>4</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1515</v>
+      </c>
+      <c r="N6" s="38"/>
+    </row>
+    <row r="7" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I7" s="1">
+        <v>5</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>1514</v>
+      </c>
+      <c r="N7" s="38"/>
+    </row>
+    <row r="8" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I8" s="1">
+        <v>6</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>1517</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>1512</v>
+      </c>
+      <c r="N8" s="38"/>
+    </row>
+    <row r="9" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I9" s="1">
+        <v>7</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>1518</v>
+      </c>
+      <c r="K9" s="1">
+        <v>60000</v>
+      </c>
+      <c r="N9" s="38"/>
+    </row>
+    <row r="10" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I10" s="1">
+        <v>8</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>1519</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>1520</v>
+      </c>
+      <c r="N10" s="38"/>
+    </row>
+    <row r="11" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I11" s="1">
+        <v>10</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>1521</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>1522</v>
+      </c>
+      <c r="N11" s="38"/>
+    </row>
+    <row r="12" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N12" s="38"/>
+    </row>
+    <row r="13" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J13" s="1" t="s">
+        <v>1523</v>
+      </c>
+      <c r="N13" s="38"/>
+      <c r="O13" s="1" t="s">
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N14" s="7"/>
+    </row>
+    <row r="15" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J15" s="1" t="s">
+        <v>1525</v>
+      </c>
+      <c r="N15" s="39" t="s">
+        <v>1526</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>1529</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>1530</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>1531</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>1532</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>1537</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>1538</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>1539</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1540</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>1541</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>1542</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>1543</v>
+      </c>
+      <c r="M18" s="1" t="s">
+        <v>1544</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="C19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="N19" s="7" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>1548</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>1549</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>1550</v>
+      </c>
+      <c r="M20" s="1" t="s">
+        <v>1551</v>
+      </c>
+      <c r="N20" s="7"/>
+    </row>
+    <row r="21" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="37" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1552</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>1553</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>1554</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>1555</v>
+      </c>
+      <c r="M21" s="1" t="s">
+        <v>1556</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>1557</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1558</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>1559</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>1560</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>1561</v>
+      </c>
+      <c r="M22" s="1" t="s">
+        <v>1562</v>
+      </c>
+      <c r="N22" s="7"/>
+    </row>
+    <row r="23" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J23" s="7"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="I24" s="1" t="s">
+        <v>1563</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>1564</v>
+      </c>
+      <c r="N24" s="7"/>
+    </row>
+    <row r="25" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J25" s="7" t="s">
+        <v>1565</v>
+      </c>
+      <c r="N25" s="7"/>
+    </row>
+    <row r="26" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="J26" s="7"/>
+      <c r="N26" s="7"/>
+    </row>
+    <row r="27" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="N27" s="7"/>
+    </row>
+    <row r="28" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="1" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="N28" s="7"/>
+      <c r="P28" s="7"/>
+    </row>
+    <row r="29" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>1568</v>
+      </c>
+      <c r="G29" s="1">
+        <v>3</v>
+      </c>
+      <c r="L29" s="1" t="s">
+        <v>1569</v>
+      </c>
+      <c r="M29" s="1" t="s">
+        <v>1570</v>
+      </c>
+      <c r="N29" s="7"/>
+      <c r="O29" s="1">
+        <v>1</v>
+      </c>
+      <c r="P29" s="7" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="1" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B30" s="1">
+        <v>2</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G30" s="1">
+        <v>2</v>
+      </c>
+      <c r="M30" s="1" t="s">
+        <v>1574</v>
+      </c>
+      <c r="N30" s="7"/>
+      <c r="O30" s="1">
+        <v>2</v>
+      </c>
+      <c r="P30" s="7" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="1" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B31" s="1">
+        <v>2</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G31" s="22">
+        <v>2</v>
+      </c>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1" t="s">
+        <v>1578</v>
+      </c>
+      <c r="N31" s="38"/>
+      <c r="O31" s="1">
+        <v>3</v>
+      </c>
+      <c r="P31" s="7" t="s">
+        <v>1579</v>
+      </c>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+    </row>
+    <row r="32" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B32" s="1">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1581</v>
+      </c>
+      <c r="G32" s="1">
+        <v>2</v>
+      </c>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="1">
+        <v>4</v>
+      </c>
+      <c r="P32" s="38"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+    </row>
+    <row r="33" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="1" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B33" s="1">
+        <v>10</v>
+      </c>
+      <c r="G33" s="1">
+        <v>1</v>
+      </c>
+      <c r="I33">
+        <v>10</v>
+      </c>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="5"/>
+      <c r="P33" s="5"/>
+      <c r="Q33" s="5"/>
+      <c r="R33" s="5"/>
+    </row>
+    <row r="34" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B34" s="1">
+        <v>10</v>
+      </c>
+      <c r="G34" s="1">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B35" s="1">
+        <v>10</v>
+      </c>
+      <c r="G35" s="1">
+        <v>1</v>
+      </c>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+    </row>
+    <row r="36" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="1" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B36" s="1">
+        <v>10</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+      <c r="R36" s="5"/>
+    </row>
+    <row r="37" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="1" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B37" s="1">
+        <v>10</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>1587</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>1588</v>
+      </c>
+      <c r="N37" s="38"/>
+      <c r="O37" s="1">
+        <v>1</v>
+      </c>
+      <c r="P37" s="5"/>
+      <c r="Q37" s="5"/>
+      <c r="R37" s="5"/>
+    </row>
+    <row r="38" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="L38" s="1"/>
+      <c r="M38" s="1" t="s">
+        <v>1589</v>
+      </c>
+      <c r="N38" s="38"/>
+      <c r="O38" s="1">
+        <v>2</v>
+      </c>
+      <c r="P38" s="5"/>
+      <c r="Q38" s="5"/>
+      <c r="R38" s="5"/>
+    </row>
+    <row r="39" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="5"/>
+      <c r="Q39" s="5"/>
+      <c r="R39" s="5"/>
+    </row>
+    <row r="40" spans="1:18" ht="20.100000000000001" customHeight="1">
+      <c r="N40" s="38"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="5"/>
+      <c r="Q40" s="5"/>
+      <c r="R40" s="5"/>
+    </row>
+    <row r="41" spans="1:18">
+      <c r="N41" s="38"/>
+      <c r="O41" s="5"/>
+      <c r="P41" s="5"/>
+      <c r="Q41" s="5"/>
+      <c r="R41" s="5"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="B1:AC50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -14678,7 +15786,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="B1:X192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -19236,7 +20344,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="B1:U50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -19933,7 +21041,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:P60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -20313,7 +21421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:AX100"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -26242,7 +27350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:AJ140"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -30721,7 +31829,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:X120"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -34517,7 +35625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:AV200"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -44823,7 +45931,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:U54"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -46716,7 +47824,947 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DDFD87B-B2E7-4251-A15A-FA4BBE5E0E8F}">
+  <dimension ref="B1:L123"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="2" max="3" width="29" style="13" customWidth="1"/>
+    <col min="4" max="4" width="102.25" style="13" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="58.75" customWidth="1"/>
+    <col min="10" max="10" width="36.875" customWidth="1"/>
+    <col min="11" max="11" width="17.5" customWidth="1"/>
+    <col min="12" max="12" width="26.25" customWidth="1"/>
+    <col min="15" max="15" width="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1" t="s">
+        <v>3062</v>
+      </c>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B2" s="118" t="s">
+        <v>2956</v>
+      </c>
+      <c r="C2" s="118"/>
+      <c r="D2" s="118" t="s">
+        <v>2957</v>
+      </c>
+      <c r="G2" s="119" t="s">
+        <v>3042</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>3043</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>3059</v>
+      </c>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+    </row>
+    <row r="3" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B3" s="1" t="s">
+        <v>2958</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>2959</v>
+      </c>
+      <c r="G3" s="119"/>
+      <c r="H3" s="1" t="s">
+        <v>3044</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>3060</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+    </row>
+    <row r="4" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B4" s="1" t="s">
+        <v>2960</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>2962</v>
+      </c>
+      <c r="G4" s="119"/>
+      <c r="H4" s="1" t="s">
+        <v>3048</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>3055</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>3056</v>
+      </c>
+      <c r="K4" s="1"/>
+    </row>
+    <row r="5" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B5" s="1" t="s">
+        <v>2961</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>2963</v>
+      </c>
+      <c r="G5" s="119"/>
+      <c r="H5" s="1" t="s">
+        <v>3045</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>3057</v>
+      </c>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+    </row>
+    <row r="6" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B6" s="46" t="s">
+        <v>2964</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D6" s="46" t="s">
+        <v>2969</v>
+      </c>
+      <c r="G6" s="119"/>
+      <c r="H6" s="1" t="s">
+        <v>3046</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>3058</v>
+      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+    </row>
+    <row r="7" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B7" s="46" t="s">
+        <v>2967</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D7" s="46" t="s">
+        <v>2968</v>
+      </c>
+      <c r="G7" s="119"/>
+      <c r="H7" s="1" t="s">
+        <v>3047</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>3061</v>
+      </c>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B8" s="1" t="s">
+        <v>2965</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>2966</v>
+      </c>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B9" s="1" t="s">
+        <v>2970</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>2975</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>2971</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B10" s="1" t="s">
+        <v>2972</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>2973</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="1" t="s">
+        <v>3083</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>3082</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B11" s="1" t="s">
+        <v>2982</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>2983</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="119" t="s">
+        <v>3063</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>3064</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>3075</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>3076</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>3064</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>3086</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B12" s="1" t="s">
+        <v>2978</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>2979</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="1" t="s">
+        <v>3065</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>3074</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>3077</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>3065</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>3088</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B13" s="1" t="s">
+        <v>2980</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>2981</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="1" t="s">
+        <v>3066</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>3073</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>3034</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>3066</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>3084</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B14" s="1" t="s">
+        <v>2991</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>2992</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="1" t="s">
+        <v>3067</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>3068</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3035</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>3067</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>3087</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B15" s="1" t="s">
+        <v>2376</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>3003</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="1" t="s">
+        <v>3069</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>3070</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>3081</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>3069</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>3085</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="20.100000000000001" customHeight="1">
+      <c r="B16" s="1" t="s">
+        <v>3004</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>3078</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3"/>
+    </row>
+    <row r="17" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>3005</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>3006</v>
+      </c>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B18" s="1" t="s">
+        <v>3013</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3014</v>
+      </c>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1">
+        <f>4*4*4</f>
+        <v>64</v>
+      </c>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B19" s="1" t="s">
+        <v>3028</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>3031</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>3029</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>3030</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B21" s="1" t="s">
+        <v>3034</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>3036</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B22" s="1" t="s">
+        <v>3035</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>3037</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B23" s="1" t="s">
+        <v>3040</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3041</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B24" s="1" t="s">
+        <v>3038</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>3039</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B25" s="1" t="s">
+        <v>3051</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>3052</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B26" s="1" t="s">
+        <v>3053</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>3054</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>2993</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>2994</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B28" s="1" t="s">
+        <v>2995</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>2996</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B29" s="1" t="s">
+        <v>2974</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>2977</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B30" s="1" t="s">
+        <v>3032</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B31" s="1" t="s">
+        <v>3079</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>3080</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" ht="20.100000000000001" customHeight="1">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B33" s="1" t="s">
+        <v>2984</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>2990</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>2989</v>
+      </c>
+    </row>
+    <row r="34" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B34" s="1" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="35" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B35" s="1" t="s">
+        <v>3050</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>2986</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B37" s="1" t="s">
+        <v>2987</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B38" s="1" t="s">
+        <v>2988</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>2990</v>
+      </c>
+    </row>
+    <row r="39" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>2997</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="40" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B40" s="1" t="s">
+        <v>2999</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="41" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B41" s="1" t="s">
+        <v>3049</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B42" s="1" t="s">
+        <v>3000</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B43" s="1" t="s">
+        <v>3001</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" ht="20.100000000000001" customHeight="1">
+      <c r="B44" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>2998</v>
+      </c>
+    </row>
+    <row r="45" spans="2:6" ht="20.100000000000001" customHeight="1"/>
+    <row r="46" spans="2:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1"/>
+      <c r="D46" s="1"/>
+    </row>
+    <row r="47" spans="2:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B47" s="1"/>
+      <c r="C47" s="1"/>
+      <c r="D47" s="1"/>
+    </row>
+    <row r="48" spans="2:6" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+    </row>
+    <row r="49" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B49" s="1"/>
+      <c r="C49" s="1"/>
+      <c r="D49" s="1"/>
+    </row>
+    <row r="50" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B50" s="1"/>
+      <c r="C50" s="1"/>
+      <c r="D50" s="1"/>
+    </row>
+    <row r="51" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B51" s="4" t="s">
+        <v>3015</v>
+      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="4" t="s">
+        <v>3025</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B52" s="1" t="s">
+        <v>3016</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>3017</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B53" s="1" t="s">
+        <v>3019</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>3020</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B54" s="1" t="s">
+        <v>3021</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>3022</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B55" s="1" t="s">
+        <v>3023</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>3024</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B56" s="1" t="s">
+        <v>3026</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3018</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>3027</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="D57" s="1"/>
+    </row>
+    <row r="58" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B58" s="1" t="s">
+        <v>3071</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>3072</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+    </row>
+    <row r="60" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+    </row>
+    <row r="61" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+    </row>
+    <row r="62" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+    </row>
+    <row r="63" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B63" s="1" t="s">
+        <v>3007</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>2976</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>3009</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B64" s="1" t="s">
+        <v>3011</v>
+      </c>
+      <c r="C64" s="1"/>
+      <c r="D64" s="5" t="s">
+        <v>3008</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B65" s="1" t="s">
+        <v>3012</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="5" t="s">
+        <v>3010</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+    </row>
+    <row r="67" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+    </row>
+    <row r="68" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+    </row>
+    <row r="69" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+    </row>
+    <row r="70" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+    </row>
+    <row r="71" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+    </row>
+    <row r="72" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+    </row>
+    <row r="73" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+    </row>
+    <row r="74" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+    </row>
+    <row r="75" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+    </row>
+    <row r="76" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+    </row>
+    <row r="77" spans="2:4" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+    </row>
+    <row r="78" spans="2:4" ht="20.100000000000001" customHeight="1"/>
+    <row r="79" spans="2:4" ht="20.100000000000001" customHeight="1"/>
+    <row r="80" spans="2:4" ht="20.100000000000001" customHeight="1"/>
+    <row r="81" ht="20.100000000000001" customHeight="1"/>
+    <row r="82" ht="20.100000000000001" customHeight="1"/>
+    <row r="83" ht="20.100000000000001" customHeight="1"/>
+    <row r="84" ht="20.100000000000001" customHeight="1"/>
+    <row r="85" ht="20.100000000000001" customHeight="1"/>
+    <row r="86" ht="20.100000000000001" customHeight="1"/>
+    <row r="87" ht="20.100000000000001" customHeight="1"/>
+    <row r="88" ht="20.100000000000001" customHeight="1"/>
+    <row r="89" ht="20.100000000000001" customHeight="1"/>
+    <row r="90" ht="20.100000000000001" customHeight="1"/>
+    <row r="91" ht="20.100000000000001" customHeight="1"/>
+    <row r="92" ht="20.100000000000001" customHeight="1"/>
+    <row r="93" ht="20.100000000000001" customHeight="1"/>
+    <row r="94" ht="20.100000000000001" customHeight="1"/>
+    <row r="95" ht="20.100000000000001" customHeight="1"/>
+    <row r="96" ht="20.100000000000001" customHeight="1"/>
+    <row r="97" ht="20.100000000000001" customHeight="1"/>
+    <row r="98" ht="20.100000000000001" customHeight="1"/>
+    <row r="99" ht="20.100000000000001" customHeight="1"/>
+    <row r="100" ht="20.100000000000001" customHeight="1"/>
+    <row r="101" ht="20.100000000000001" customHeight="1"/>
+    <row r="102" ht="20.100000000000001" customHeight="1"/>
+    <row r="103" ht="20.100000000000001" customHeight="1"/>
+    <row r="104" ht="20.100000000000001" customHeight="1"/>
+    <row r="105" ht="20.100000000000001" customHeight="1"/>
+    <row r="106" ht="20.100000000000001" customHeight="1"/>
+    <row r="107" ht="20.100000000000001" customHeight="1"/>
+    <row r="108" ht="20.100000000000001" customHeight="1"/>
+    <row r="109" ht="20.100000000000001" customHeight="1"/>
+    <row r="110" ht="20.100000000000001" customHeight="1"/>
+    <row r="111" ht="20.100000000000001" customHeight="1"/>
+    <row r="112" ht="20.100000000000001" customHeight="1"/>
+    <row r="113" ht="20.100000000000001" customHeight="1"/>
+    <row r="114" ht="20.100000000000001" customHeight="1"/>
+    <row r="115" ht="20.100000000000001" customHeight="1"/>
+    <row r="116" ht="20.100000000000001" customHeight="1"/>
+    <row r="117" ht="20.100000000000001" customHeight="1"/>
+    <row r="118" ht="20.100000000000001" customHeight="1"/>
+    <row r="119" ht="20.100000000000001" customHeight="1"/>
+    <row r="120" ht="20.100000000000001" customHeight="1"/>
+    <row r="121" ht="20.100000000000001" customHeight="1"/>
+    <row r="122" ht="20.100000000000001" customHeight="1"/>
+    <row r="123" ht="20.100000000000001" customHeight="1"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="G2:G7"/>
+    <mergeCell ref="G11:G15"/>
+  </mergeCells>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="C1:P41"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -46908,2078 +48956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H71"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="7" width="9" style="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A1" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1">
-        <v>5</v>
-      </c>
-      <c r="C2" s="1">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1">
-        <f>B2*[1]属性总表!$E$5</f>
-        <v>5250</v>
-      </c>
-      <c r="E2" s="1">
-        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
-        <v>500</v>
-      </c>
-      <c r="F2" s="1">
-        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="G2" s="1">
-        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
-        <v>150</v>
-      </c>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1">
-        <f>B2+0.25</f>
-        <v>5.25</v>
-      </c>
-      <c r="C3" s="1">
-        <f>C2+0.12</f>
-        <v>5.12</v>
-      </c>
-      <c r="D3" s="1">
-        <f>B3*[1]属性总表!$E$5</f>
-        <v>5512.5</v>
-      </c>
-      <c r="E3" s="1">
-        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
-        <v>512</v>
-      </c>
-      <c r="F3" s="1">
-        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="G3" s="1">
-        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
-        <v>154</v>
-      </c>
-      <c r="H3" s="1">
-        <f>D3-D2</f>
-        <v>262.5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1">
-        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
-        <v>5.5</v>
-      </c>
-      <c r="C4" s="1">
-        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
-        <v>5.24</v>
-      </c>
-      <c r="D4" s="1">
-        <f>B4*[1]属性总表!$E$5</f>
-        <v>5775</v>
-      </c>
-      <c r="E4" s="1">
-        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
-        <v>524</v>
-      </c>
-      <c r="F4" s="1">
-        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="G4" s="1">
-        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
-        <v>157</v>
-      </c>
-      <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1">
-        <f t="shared" si="0"/>
-        <v>5.75</v>
-      </c>
-      <c r="C5" s="1">
-        <f t="shared" si="1"/>
-        <v>5.36</v>
-      </c>
-      <c r="D5" s="1">
-        <f>B5*[1]属性总表!$E$5</f>
-        <v>6037.5</v>
-      </c>
-      <c r="E5" s="1">
-        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
-        <v>536</v>
-      </c>
-      <c r="F5" s="1">
-        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
-        <v>161</v>
-      </c>
-      <c r="G5" s="1">
-        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
-        <v>161</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <f t="shared" si="1"/>
-        <v>5.48</v>
-      </c>
-      <c r="D6" s="1">
-        <f>B6*[1]属性总表!$E$5</f>
-        <v>6300</v>
-      </c>
-      <c r="E6" s="1">
-        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
-        <v>548</v>
-      </c>
-      <c r="F6" s="1">
-        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
-        <v>164</v>
-      </c>
-      <c r="G6" s="1">
-        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <f t="shared" si="0"/>
-        <v>6.25</v>
-      </c>
-      <c r="C7" s="1">
-        <f t="shared" si="1"/>
-        <v>5.6000000000000005</v>
-      </c>
-      <c r="D7" s="1">
-        <f>B7*[1]属性总表!$E$5</f>
-        <v>6562.5</v>
-      </c>
-      <c r="E7" s="1">
-        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
-        <v>560</v>
-      </c>
-      <c r="F7" s="1">
-        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
-        <v>168</v>
-      </c>
-      <c r="G7" s="1">
-        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
-        <v>168</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <f t="shared" si="0"/>
-        <v>6.5</v>
-      </c>
-      <c r="C8" s="1">
-        <f t="shared" si="1"/>
-        <v>5.7200000000000006</v>
-      </c>
-      <c r="D8" s="1">
-        <f>B8*[1]属性总表!$E$5</f>
-        <v>6825</v>
-      </c>
-      <c r="E8" s="1">
-        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
-        <v>572</v>
-      </c>
-      <c r="F8" s="1">
-        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
-        <v>172</v>
-      </c>
-      <c r="G8" s="1">
-        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1">
-        <f t="shared" si="0"/>
-        <v>6.75</v>
-      </c>
-      <c r="C9" s="1">
-        <f t="shared" si="1"/>
-        <v>5.8400000000000007</v>
-      </c>
-      <c r="D9" s="1">
-        <f>B9*[1]属性总表!$E$5</f>
-        <v>7087.5</v>
-      </c>
-      <c r="E9" s="1">
-        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
-        <v>584</v>
-      </c>
-      <c r="F9" s="1">
-        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
-        <v>175</v>
-      </c>
-      <c r="G9" s="1">
-        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
-        <v>175</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="C10" s="1">
-        <f t="shared" si="1"/>
-        <v>5.9600000000000009</v>
-      </c>
-      <c r="D10" s="1">
-        <f>B10*[1]属性总表!$E$5</f>
-        <v>7350</v>
-      </c>
-      <c r="E10" s="1">
-        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
-        <v>596</v>
-      </c>
-      <c r="F10" s="1">
-        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
-        <v>179</v>
-      </c>
-      <c r="G10" s="1">
-        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1">
-        <f t="shared" si="0"/>
-        <v>7.25</v>
-      </c>
-      <c r="C11" s="1">
-        <f t="shared" si="1"/>
-        <v>6.080000000000001</v>
-      </c>
-      <c r="D11" s="1">
-        <f>B11*[1]属性总表!$E$5</f>
-        <v>7612.5</v>
-      </c>
-      <c r="E11" s="1">
-        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
-        <v>608</v>
-      </c>
-      <c r="F11" s="1">
-        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
-        <v>182</v>
-      </c>
-      <c r="G11" s="1">
-        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1">
-        <f t="shared" si="0"/>
-        <v>7.5</v>
-      </c>
-      <c r="C12" s="1">
-        <f t="shared" si="1"/>
-        <v>6.2000000000000011</v>
-      </c>
-      <c r="D12" s="1">
-        <f>B12*[1]属性总表!$E$5</f>
-        <v>7875</v>
-      </c>
-      <c r="E12" s="1">
-        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
-        <v>620</v>
-      </c>
-      <c r="F12" s="1">
-        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
-        <v>186</v>
-      </c>
-      <c r="G12" s="1">
-        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1">
-        <f t="shared" si="0"/>
-        <v>7.75</v>
-      </c>
-      <c r="C13" s="1">
-        <f t="shared" si="1"/>
-        <v>6.3200000000000012</v>
-      </c>
-      <c r="D13" s="1">
-        <f>B13*[1]属性总表!$E$5</f>
-        <v>8137.5</v>
-      </c>
-      <c r="E13" s="1">
-        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
-        <v>632</v>
-      </c>
-      <c r="F13" s="1">
-        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
-        <v>190</v>
-      </c>
-      <c r="G13" s="1">
-        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
-        <v>190</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="C14" s="1">
-        <f t="shared" si="1"/>
-        <v>6.4400000000000013</v>
-      </c>
-      <c r="D14" s="1">
-        <f>B14*[1]属性总表!$E$5</f>
-        <v>8400</v>
-      </c>
-      <c r="E14" s="1">
-        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
-        <v>644</v>
-      </c>
-      <c r="F14" s="1">
-        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
-        <v>193</v>
-      </c>
-      <c r="G14" s="1">
-        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
-        <v>193</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1">
-        <f t="shared" si="0"/>
-        <v>8.25</v>
-      </c>
-      <c r="C15" s="1">
-        <f t="shared" si="1"/>
-        <v>6.5600000000000014</v>
-      </c>
-      <c r="D15" s="1">
-        <f>B15*[1]属性总表!$E$5</f>
-        <v>8662.5</v>
-      </c>
-      <c r="E15" s="1">
-        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
-        <v>656</v>
-      </c>
-      <c r="F15" s="1">
-        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
-        <v>197</v>
-      </c>
-      <c r="G15" s="1">
-        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
-        <v>197</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1">
-        <f t="shared" si="0"/>
-        <v>8.5</v>
-      </c>
-      <c r="C16" s="1">
-        <f t="shared" si="1"/>
-        <v>6.6800000000000015</v>
-      </c>
-      <c r="D16" s="1">
-        <f>B16*[1]属性总表!$E$5</f>
-        <v>8925</v>
-      </c>
-      <c r="E16" s="1">
-        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
-        <v>668</v>
-      </c>
-      <c r="F16" s="1">
-        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
-        <v>200</v>
-      </c>
-      <c r="G16" s="1">
-        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
-        <v>200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1">
-        <f t="shared" si="0"/>
-        <v>8.75</v>
-      </c>
-      <c r="C17" s="1">
-        <f t="shared" si="1"/>
-        <v>6.8000000000000016</v>
-      </c>
-      <c r="D17" s="1">
-        <f>B17*[1]属性总表!$E$5</f>
-        <v>9187.5</v>
-      </c>
-      <c r="E17" s="1">
-        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
-        <v>680</v>
-      </c>
-      <c r="F17" s="1">
-        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
-        <v>204</v>
-      </c>
-      <c r="G17" s="1">
-        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
-        <v>204</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="C18" s="1">
-        <f t="shared" si="1"/>
-        <v>6.9200000000000017</v>
-      </c>
-      <c r="D18" s="1">
-        <f>B18*[1]属性总表!$E$5</f>
-        <v>9450</v>
-      </c>
-      <c r="E18" s="1">
-        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
-        <v>692</v>
-      </c>
-      <c r="F18" s="1">
-        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
-        <v>208</v>
-      </c>
-      <c r="G18" s="1">
-        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
-        <v>208</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1">
-        <f t="shared" si="0"/>
-        <v>9.25</v>
-      </c>
-      <c r="C19" s="1">
-        <f t="shared" si="1"/>
-        <v>7.0400000000000018</v>
-      </c>
-      <c r="D19" s="1">
-        <f>B19*[1]属性总表!$E$5</f>
-        <v>9712.5</v>
-      </c>
-      <c r="E19" s="1">
-        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
-        <v>704</v>
-      </c>
-      <c r="F19" s="1">
-        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
-        <v>211</v>
-      </c>
-      <c r="G19" s="1">
-        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
-        <v>211</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1">
-        <f t="shared" si="0"/>
-        <v>9.5</v>
-      </c>
-      <c r="C20" s="1">
-        <f t="shared" si="1"/>
-        <v>7.1600000000000019</v>
-      </c>
-      <c r="D20" s="1">
-        <f>B20*[1]属性总表!$E$5</f>
-        <v>9975</v>
-      </c>
-      <c r="E20" s="1">
-        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
-        <v>716</v>
-      </c>
-      <c r="F20" s="1">
-        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
-        <v>215</v>
-      </c>
-      <c r="G20" s="1">
-        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
-        <v>215</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1">
-        <f t="shared" si="0"/>
-        <v>9.75</v>
-      </c>
-      <c r="C21" s="1">
-        <f t="shared" si="1"/>
-        <v>7.280000000000002</v>
-      </c>
-      <c r="D21" s="1">
-        <f>B21*[1]属性总表!$E$5</f>
-        <v>10237.5</v>
-      </c>
-      <c r="E21" s="1">
-        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
-        <v>728</v>
-      </c>
-      <c r="F21" s="1">
-        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
-        <v>218</v>
-      </c>
-      <c r="G21" s="1">
-        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
-        <v>218</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="1">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C22" s="1">
-        <f t="shared" si="1"/>
-        <v>7.4000000000000021</v>
-      </c>
-      <c r="D22" s="1">
-        <f>B22*[1]属性总表!$E$5</f>
-        <v>10500</v>
-      </c>
-      <c r="E22" s="1">
-        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
-        <v>740</v>
-      </c>
-      <c r="F22" s="1">
-        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
-        <v>222</v>
-      </c>
-      <c r="G22" s="1">
-        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
-        <v>222</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1">
-        <f t="shared" si="0"/>
-        <v>10.25</v>
-      </c>
-      <c r="C23" s="1">
-        <f t="shared" si="1"/>
-        <v>7.5200000000000022</v>
-      </c>
-      <c r="D23" s="1">
-        <f>B23*[1]属性总表!$E$5</f>
-        <v>10762.5</v>
-      </c>
-      <c r="E23" s="1">
-        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
-        <v>752</v>
-      </c>
-      <c r="F23" s="1">
-        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
-        <v>226</v>
-      </c>
-      <c r="G23" s="1">
-        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
-        <v>226</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1">
-        <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="C24" s="1">
-        <f t="shared" si="1"/>
-        <v>7.6400000000000023</v>
-      </c>
-      <c r="D24" s="1">
-        <f>B24*[1]属性总表!$E$5</f>
-        <v>11025</v>
-      </c>
-      <c r="E24" s="1">
-        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
-        <v>764</v>
-      </c>
-      <c r="F24" s="1">
-        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
-        <v>229</v>
-      </c>
-      <c r="G24" s="1">
-        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
-        <v>229</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1">
-        <f t="shared" si="0"/>
-        <v>10.75</v>
-      </c>
-      <c r="C25" s="1">
-        <f t="shared" si="1"/>
-        <v>7.7600000000000025</v>
-      </c>
-      <c r="D25" s="1">
-        <f>B25*[1]属性总表!$E$5</f>
-        <v>11287.5</v>
-      </c>
-      <c r="E25" s="1">
-        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
-        <v>776</v>
-      </c>
-      <c r="F25" s="1">
-        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
-        <v>233</v>
-      </c>
-      <c r="G25" s="1">
-        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
-        <v>233</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="1">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="C26" s="1">
-        <f t="shared" si="1"/>
-        <v>7.8800000000000026</v>
-      </c>
-      <c r="D26" s="1">
-        <f>B26*[1]属性总表!$E$5</f>
-        <v>11550</v>
-      </c>
-      <c r="E26" s="1">
-        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
-        <v>788</v>
-      </c>
-      <c r="F26" s="1">
-        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
-        <v>236</v>
-      </c>
-      <c r="G26" s="1">
-        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
-        <v>236</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1">
-        <f t="shared" si="0"/>
-        <v>11.25</v>
-      </c>
-      <c r="C27" s="1">
-        <f t="shared" si="1"/>
-        <v>8.0000000000000018</v>
-      </c>
-      <c r="D27" s="1">
-        <f>B27*[1]属性总表!$E$5</f>
-        <v>11812.5</v>
-      </c>
-      <c r="E27" s="1">
-        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
-        <v>800</v>
-      </c>
-      <c r="F27" s="1">
-        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
-        <v>240</v>
-      </c>
-      <c r="G27" s="1">
-        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
-        <v>240</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="1">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1">
-        <f t="shared" si="0"/>
-        <v>11.5</v>
-      </c>
-      <c r="C28" s="1">
-        <f t="shared" si="1"/>
-        <v>8.120000000000001</v>
-      </c>
-      <c r="D28" s="1">
-        <f>B28*[1]属性总表!$E$5</f>
-        <v>12075</v>
-      </c>
-      <c r="E28" s="1">
-        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
-        <v>812</v>
-      </c>
-      <c r="F28" s="1">
-        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
-        <v>244</v>
-      </c>
-      <c r="G28" s="1">
-        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
-        <v>244</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="1">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <f t="shared" si="0"/>
-        <v>11.75</v>
-      </c>
-      <c r="C29" s="1">
-        <f t="shared" si="1"/>
-        <v>8.24</v>
-      </c>
-      <c r="D29" s="1">
-        <f>B29*[1]属性总表!$E$5</f>
-        <v>12337.5</v>
-      </c>
-      <c r="E29" s="1">
-        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
-        <v>824</v>
-      </c>
-      <c r="F29" s="1">
-        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
-        <v>247</v>
-      </c>
-      <c r="G29" s="1">
-        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
-        <v>247</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="1">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C30" s="1">
-        <f t="shared" si="1"/>
-        <v>8.36</v>
-      </c>
-      <c r="D30" s="1">
-        <f>B30*[1]属性总表!$E$5</f>
-        <v>12600</v>
-      </c>
-      <c r="E30" s="1">
-        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
-        <v>836</v>
-      </c>
-      <c r="F30" s="1">
-        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
-        <v>251</v>
-      </c>
-      <c r="G30" s="1">
-        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
-        <v>251</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="1">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1">
-        <f t="shared" si="0"/>
-        <v>12.25</v>
-      </c>
-      <c r="C31" s="1">
-        <f t="shared" si="1"/>
-        <v>8.4799999999999986</v>
-      </c>
-      <c r="D31" s="1">
-        <f>B31*[1]属性总表!$E$5</f>
-        <v>12862.5</v>
-      </c>
-      <c r="E31" s="1">
-        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
-        <v>848</v>
-      </c>
-      <c r="F31" s="1">
-        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
-        <v>254</v>
-      </c>
-      <c r="G31" s="1">
-        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
-        <v>254</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="1">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1">
-        <f t="shared" si="0"/>
-        <v>12.5</v>
-      </c>
-      <c r="C32" s="1">
-        <f t="shared" si="1"/>
-        <v>8.5999999999999979</v>
-      </c>
-      <c r="D32" s="1">
-        <f>B32*[1]属性总表!$E$5</f>
-        <v>13125</v>
-      </c>
-      <c r="E32" s="1">
-        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
-        <v>860</v>
-      </c>
-      <c r="F32" s="1">
-        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
-        <v>258</v>
-      </c>
-      <c r="G32" s="1">
-        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
-        <v>258</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="1">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1">
-        <f t="shared" si="0"/>
-        <v>12.75</v>
-      </c>
-      <c r="C33" s="1">
-        <f t="shared" si="1"/>
-        <v>8.7199999999999971</v>
-      </c>
-      <c r="D33" s="1">
-        <f>B33*[1]属性总表!$E$5</f>
-        <v>13387.5</v>
-      </c>
-      <c r="E33" s="1">
-        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
-        <v>872</v>
-      </c>
-      <c r="F33" s="1">
-        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
-        <v>262</v>
-      </c>
-      <c r="G33" s="1">
-        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
-        <v>262</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="1">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="C34" s="1">
-        <f t="shared" si="1"/>
-        <v>8.8399999999999963</v>
-      </c>
-      <c r="D34" s="1">
-        <f>B34*[1]属性总表!$E$5</f>
-        <v>13650</v>
-      </c>
-      <c r="E34" s="1">
-        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
-        <v>884</v>
-      </c>
-      <c r="F34" s="1">
-        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
-        <v>265</v>
-      </c>
-      <c r="G34" s="1">
-        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
-        <v>265</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="1">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1">
-        <f t="shared" si="0"/>
-        <v>13.25</v>
-      </c>
-      <c r="C35" s="1">
-        <f t="shared" si="1"/>
-        <v>8.9599999999999955</v>
-      </c>
-      <c r="D35" s="1">
-        <f>B35*[1]属性总表!$E$5</f>
-        <v>13912.5</v>
-      </c>
-      <c r="E35" s="1">
-        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
-        <v>896</v>
-      </c>
-      <c r="F35" s="1">
-        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
-        <v>269</v>
-      </c>
-      <c r="G35" s="1">
-        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="1">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1">
-        <f t="shared" si="0"/>
-        <v>13.5</v>
-      </c>
-      <c r="C36" s="1">
-        <f t="shared" si="1"/>
-        <v>9.0799999999999947</v>
-      </c>
-      <c r="D36" s="1">
-        <f>B36*[1]属性总表!$E$5</f>
-        <v>14175</v>
-      </c>
-      <c r="E36" s="1">
-        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
-        <v>908</v>
-      </c>
-      <c r="F36" s="1">
-        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
-        <v>272</v>
-      </c>
-      <c r="G36" s="1">
-        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
-        <v>272</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="1">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1">
-        <f t="shared" si="0"/>
-        <v>13.75</v>
-      </c>
-      <c r="C37" s="1">
-        <f t="shared" si="1"/>
-        <v>9.199999999999994</v>
-      </c>
-      <c r="D37" s="1">
-        <f>B37*[1]属性总表!$E$5</f>
-        <v>14437.5</v>
-      </c>
-      <c r="E37" s="1">
-        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
-        <v>920</v>
-      </c>
-      <c r="F37" s="1">
-        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
-        <v>276</v>
-      </c>
-      <c r="G37" s="1">
-        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
-        <v>276</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="1">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C38" s="1">
-        <f t="shared" si="1"/>
-        <v>9.3199999999999932</v>
-      </c>
-      <c r="D38" s="1">
-        <f>B38*[1]属性总表!$E$5</f>
-        <v>14700</v>
-      </c>
-      <c r="E38" s="1">
-        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
-        <v>932</v>
-      </c>
-      <c r="F38" s="1">
-        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
-        <v>280</v>
-      </c>
-      <c r="G38" s="1">
-        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
-        <v>280</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="1">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1">
-        <f t="shared" si="0"/>
-        <v>14.25</v>
-      </c>
-      <c r="C39" s="1">
-        <f t="shared" si="1"/>
-        <v>9.4399999999999924</v>
-      </c>
-      <c r="D39" s="1">
-        <f>B39*[1]属性总表!$E$5</f>
-        <v>14962.5</v>
-      </c>
-      <c r="E39" s="1">
-        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
-        <v>944</v>
-      </c>
-      <c r="F39" s="1">
-        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
-        <v>283</v>
-      </c>
-      <c r="G39" s="1">
-        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
-        <v>283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="1">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1">
-        <f t="shared" si="0"/>
-        <v>14.5</v>
-      </c>
-      <c r="C40" s="1">
-        <f t="shared" si="1"/>
-        <v>9.5599999999999916</v>
-      </c>
-      <c r="D40" s="1">
-        <f>B40*[1]属性总表!$E$5</f>
-        <v>15225</v>
-      </c>
-      <c r="E40" s="1">
-        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
-        <v>956</v>
-      </c>
-      <c r="F40" s="1">
-        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
-        <v>287</v>
-      </c>
-      <c r="G40" s="1">
-        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="1">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1">
-        <f t="shared" si="0"/>
-        <v>14.75</v>
-      </c>
-      <c r="C41" s="1">
-        <f t="shared" si="1"/>
-        <v>9.6799999999999908</v>
-      </c>
-      <c r="D41" s="1">
-        <f>B41*[1]属性总表!$E$5</f>
-        <v>15487.5</v>
-      </c>
-      <c r="E41" s="1">
-        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
-        <v>968</v>
-      </c>
-      <c r="F41" s="1">
-        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
-        <v>290</v>
-      </c>
-      <c r="G41" s="1">
-        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="1">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="C42" s="1">
-        <f t="shared" si="1"/>
-        <v>9.7999999999999901</v>
-      </c>
-      <c r="D42" s="1">
-        <f>B42*[1]属性总表!$E$5</f>
-        <v>15750</v>
-      </c>
-      <c r="E42" s="1">
-        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
-        <v>980</v>
-      </c>
-      <c r="F42" s="1">
-        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
-        <v>294</v>
-      </c>
-      <c r="G42" s="1">
-        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
-        <v>294</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="1">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1">
-        <f t="shared" si="0"/>
-        <v>15.25</v>
-      </c>
-      <c r="C43" s="1">
-        <f t="shared" si="1"/>
-        <v>9.9199999999999893</v>
-      </c>
-      <c r="D43" s="1">
-        <f>B43*[1]属性总表!$E$5</f>
-        <v>16012.5</v>
-      </c>
-      <c r="E43" s="1">
-        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
-        <v>992</v>
-      </c>
-      <c r="F43" s="1">
-        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
-        <v>298</v>
-      </c>
-      <c r="G43" s="1">
-        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
-        <v>298</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="1">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1">
-        <f t="shared" si="0"/>
-        <v>15.5</v>
-      </c>
-      <c r="C44" s="1">
-        <f t="shared" si="1"/>
-        <v>10.039999999999988</v>
-      </c>
-      <c r="D44" s="1">
-        <f>B44*[1]属性总表!$E$5</f>
-        <v>16275</v>
-      </c>
-      <c r="E44" s="1">
-        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
-        <v>1004</v>
-      </c>
-      <c r="F44" s="1">
-        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
-        <v>301</v>
-      </c>
-      <c r="G44" s="1">
-        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
-        <v>301</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="1">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1">
-        <f t="shared" si="0"/>
-        <v>15.75</v>
-      </c>
-      <c r="C45" s="1">
-        <f t="shared" si="1"/>
-        <v>10.159999999999988</v>
-      </c>
-      <c r="D45" s="1">
-        <f>B45*[1]属性总表!$E$5</f>
-        <v>16537.5</v>
-      </c>
-      <c r="E45" s="1">
-        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
-        <v>1016</v>
-      </c>
-      <c r="F45" s="1">
-        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
-        <v>305</v>
-      </c>
-      <c r="G45" s="1">
-        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
-        <v>305</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="1">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C46" s="1">
-        <f t="shared" si="1"/>
-        <v>10.279999999999987</v>
-      </c>
-      <c r="D46" s="1">
-        <f>B46*[1]属性总表!$E$5</f>
-        <v>16800</v>
-      </c>
-      <c r="E46" s="1">
-        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
-        <v>1028</v>
-      </c>
-      <c r="F46" s="1">
-        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
-        <v>308</v>
-      </c>
-      <c r="G46" s="1">
-        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
-        <v>308</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="1">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1">
-        <f t="shared" si="0"/>
-        <v>16.25</v>
-      </c>
-      <c r="C47" s="1">
-        <f t="shared" si="1"/>
-        <v>10.399999999999986</v>
-      </c>
-      <c r="D47" s="1">
-        <f>B47*[1]属性总表!$E$5</f>
-        <v>17062.5</v>
-      </c>
-      <c r="E47" s="1">
-        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
-        <v>1040</v>
-      </c>
-      <c r="F47" s="1">
-        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
-        <v>312</v>
-      </c>
-      <c r="G47" s="1">
-        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
-        <v>312</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="1">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="C48" s="1">
-        <f t="shared" si="1"/>
-        <v>10.519999999999985</v>
-      </c>
-      <c r="D48" s="1">
-        <f>B48*[1]属性总表!$E$5</f>
-        <v>17325</v>
-      </c>
-      <c r="E48" s="1">
-        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
-        <v>1052</v>
-      </c>
-      <c r="F48" s="1">
-        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
-        <v>316</v>
-      </c>
-      <c r="G48" s="1">
-        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
-        <v>316</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="1">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1">
-        <f t="shared" si="0"/>
-        <v>16.75</v>
-      </c>
-      <c r="C49" s="1">
-        <f t="shared" si="1"/>
-        <v>10.639999999999985</v>
-      </c>
-      <c r="D49" s="1">
-        <f>B49*[1]属性总表!$E$5</f>
-        <v>17587.5</v>
-      </c>
-      <c r="E49" s="1">
-        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
-        <v>1064</v>
-      </c>
-      <c r="F49" s="1">
-        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
-        <v>319</v>
-      </c>
-      <c r="G49" s="1">
-        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
-        <v>319</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="1">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C50" s="1">
-        <f t="shared" si="1"/>
-        <v>10.759999999999984</v>
-      </c>
-      <c r="D50" s="1">
-        <f>B50*[1]属性总表!$E$5</f>
-        <v>17850</v>
-      </c>
-      <c r="E50" s="1">
-        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
-        <v>1076</v>
-      </c>
-      <c r="F50" s="1">
-        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
-        <v>323</v>
-      </c>
-      <c r="G50" s="1">
-        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
-        <v>323</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="1">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1">
-        <f t="shared" si="0"/>
-        <v>17.25</v>
-      </c>
-      <c r="C51" s="1">
-        <f t="shared" si="1"/>
-        <v>10.879999999999983</v>
-      </c>
-      <c r="D51" s="1">
-        <f>B51*[1]属性总表!$E$5</f>
-        <v>18112.5</v>
-      </c>
-      <c r="E51" s="1">
-        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
-        <v>1088</v>
-      </c>
-      <c r="F51" s="1">
-        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
-        <v>326</v>
-      </c>
-      <c r="G51" s="1">
-        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
-        <v>326</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="1">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1">
-        <f t="shared" si="0"/>
-        <v>17.5</v>
-      </c>
-      <c r="C52" s="1">
-        <f t="shared" si="1"/>
-        <v>10.999999999999982</v>
-      </c>
-      <c r="D52" s="1">
-        <f>B52*[1]属性总表!$E$5</f>
-        <v>18375</v>
-      </c>
-      <c r="E52" s="1">
-        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
-        <v>1100</v>
-      </c>
-      <c r="F52" s="1">
-        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
-        <v>330</v>
-      </c>
-      <c r="G52" s="1">
-        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
-        <v>330</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="1">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1">
-        <f t="shared" si="0"/>
-        <v>17.75</v>
-      </c>
-      <c r="C53" s="1">
-        <f t="shared" si="1"/>
-        <v>11.119999999999981</v>
-      </c>
-      <c r="D53" s="1">
-        <f>B53*[1]属性总表!$E$5</f>
-        <v>18637.5</v>
-      </c>
-      <c r="E53" s="1">
-        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
-        <v>1112</v>
-      </c>
-      <c r="F53" s="1">
-        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
-        <v>334</v>
-      </c>
-      <c r="G53" s="1">
-        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
-        <v>334</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="1">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="C54" s="1">
-        <f t="shared" si="1"/>
-        <v>11.239999999999981</v>
-      </c>
-      <c r="D54" s="1">
-        <f>B54*[1]属性总表!$E$5</f>
-        <v>18900</v>
-      </c>
-      <c r="E54" s="1">
-        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
-        <v>1124</v>
-      </c>
-      <c r="F54" s="1">
-        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
-        <v>337</v>
-      </c>
-      <c r="G54" s="1">
-        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
-        <v>337</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="1">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1">
-        <f t="shared" si="0"/>
-        <v>18.25</v>
-      </c>
-      <c r="C55" s="1">
-        <f t="shared" si="1"/>
-        <v>11.35999999999998</v>
-      </c>
-      <c r="D55" s="1">
-        <f>B55*[1]属性总表!$E$5</f>
-        <v>19162.5</v>
-      </c>
-      <c r="E55" s="1">
-        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
-        <v>1136</v>
-      </c>
-      <c r="F55" s="1">
-        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
-        <v>341</v>
-      </c>
-      <c r="G55" s="1">
-        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
-        <v>341</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="1">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1">
-        <f t="shared" si="0"/>
-        <v>18.5</v>
-      </c>
-      <c r="C56" s="1">
-        <f t="shared" si="1"/>
-        <v>11.479999999999979</v>
-      </c>
-      <c r="D56" s="1">
-        <f>B56*[1]属性总表!$E$5</f>
-        <v>19425</v>
-      </c>
-      <c r="E56" s="1">
-        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
-        <v>1148</v>
-      </c>
-      <c r="F56" s="1">
-        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
-        <v>344</v>
-      </c>
-      <c r="G56" s="1">
-        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
-        <v>344</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="1">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1">
-        <f t="shared" si="0"/>
-        <v>18.75</v>
-      </c>
-      <c r="C57" s="1">
-        <f t="shared" si="1"/>
-        <v>11.599999999999978</v>
-      </c>
-      <c r="D57" s="1">
-        <f>B57*[1]属性总表!$E$5</f>
-        <v>19687.5</v>
-      </c>
-      <c r="E57" s="1">
-        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
-        <v>1160</v>
-      </c>
-      <c r="F57" s="1">
-        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
-        <v>348</v>
-      </c>
-      <c r="G57" s="1">
-        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
-        <v>348</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="1">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="C58" s="1">
-        <f t="shared" si="1"/>
-        <v>11.719999999999978</v>
-      </c>
-      <c r="D58" s="1">
-        <f>B58*[1]属性总表!$E$5</f>
-        <v>19950</v>
-      </c>
-      <c r="E58" s="1">
-        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
-        <v>1172</v>
-      </c>
-      <c r="F58" s="1">
-        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
-        <v>352</v>
-      </c>
-      <c r="G58" s="1">
-        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
-        <v>352</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="1">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1">
-        <f t="shared" si="0"/>
-        <v>19.25</v>
-      </c>
-      <c r="C59" s="1">
-        <f t="shared" si="1"/>
-        <v>11.839999999999977</v>
-      </c>
-      <c r="D59" s="1">
-        <f>B59*[1]属性总表!$E$5</f>
-        <v>20212.5</v>
-      </c>
-      <c r="E59" s="1">
-        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
-        <v>1184</v>
-      </c>
-      <c r="F59" s="1">
-        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
-        <v>355</v>
-      </c>
-      <c r="G59" s="1">
-        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
-        <v>355</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="1">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="C60" s="1">
-        <f t="shared" si="1"/>
-        <v>11.959999999999976</v>
-      </c>
-      <c r="D60" s="1">
-        <f>B60*[1]属性总表!$E$5</f>
-        <v>20475</v>
-      </c>
-      <c r="E60" s="1">
-        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
-        <v>1196</v>
-      </c>
-      <c r="F60" s="1">
-        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
-        <v>359</v>
-      </c>
-      <c r="G60" s="1">
-        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
-        <v>359</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="1">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1">
-        <f t="shared" si="0"/>
-        <v>19.75</v>
-      </c>
-      <c r="C61" s="1">
-        <f t="shared" si="1"/>
-        <v>12.079999999999975</v>
-      </c>
-      <c r="D61" s="1">
-        <f>B61*[1]属性总表!$E$5</f>
-        <v>20737.5</v>
-      </c>
-      <c r="E61" s="1">
-        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
-        <v>1208</v>
-      </c>
-      <c r="F61" s="1">
-        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
-        <v>362</v>
-      </c>
-      <c r="G61" s="1">
-        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
-        <v>362</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="1">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="C62" s="1">
-        <f t="shared" si="1"/>
-        <v>12.199999999999974</v>
-      </c>
-      <c r="D62" s="1">
-        <f>B62*[1]属性总表!$E$5</f>
-        <v>21000</v>
-      </c>
-      <c r="E62" s="1">
-        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
-        <v>1220</v>
-      </c>
-      <c r="F62" s="1">
-        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
-        <v>366</v>
-      </c>
-      <c r="G62" s="1">
-        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
-        <v>366</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="1">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1">
-        <f t="shared" si="0"/>
-        <v>20.25</v>
-      </c>
-      <c r="C63" s="1">
-        <f t="shared" si="1"/>
-        <v>12.319999999999974</v>
-      </c>
-      <c r="D63" s="1">
-        <f>B63*[1]属性总表!$E$5</f>
-        <v>21262.5</v>
-      </c>
-      <c r="E63" s="1">
-        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
-        <v>1232</v>
-      </c>
-      <c r="F63" s="1">
-        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
-        <v>370</v>
-      </c>
-      <c r="G63" s="1">
-        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
-        <v>370</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="1">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1">
-        <f t="shared" si="0"/>
-        <v>20.5</v>
-      </c>
-      <c r="C64" s="1">
-        <f t="shared" si="1"/>
-        <v>12.439999999999973</v>
-      </c>
-      <c r="D64" s="1">
-        <f>B64*[1]属性总表!$E$5</f>
-        <v>21525</v>
-      </c>
-      <c r="E64" s="1">
-        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
-        <v>1244</v>
-      </c>
-      <c r="F64" s="1">
-        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
-        <v>373</v>
-      </c>
-      <c r="G64" s="1">
-        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
-        <v>373</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="1">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1">
-        <f t="shared" si="0"/>
-        <v>20.75</v>
-      </c>
-      <c r="C65" s="1">
-        <f t="shared" si="1"/>
-        <v>12.559999999999972</v>
-      </c>
-      <c r="D65" s="1">
-        <f>B65*[1]属性总表!$E$5</f>
-        <v>21787.5</v>
-      </c>
-      <c r="E65" s="1">
-        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
-        <v>1256</v>
-      </c>
-      <c r="F65" s="1">
-        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
-        <v>377</v>
-      </c>
-      <c r="G65" s="1">
-        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
-        <v>377</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="1">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="C66" s="1">
-        <f t="shared" si="1"/>
-        <v>12.679999999999971</v>
-      </c>
-      <c r="D66" s="1">
-        <f>B66*[1]属性总表!$E$5</f>
-        <v>22050</v>
-      </c>
-      <c r="E66" s="1">
-        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
-        <v>1268</v>
-      </c>
-      <c r="F66" s="1">
-        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
-        <v>380</v>
-      </c>
-      <c r="G66" s="1">
-        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
-        <v>380</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="1">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1">
-        <f t="shared" si="0"/>
-        <v>21.25</v>
-      </c>
-      <c r="C67" s="1">
-        <f t="shared" si="1"/>
-        <v>12.799999999999971</v>
-      </c>
-      <c r="D67" s="1">
-        <f>B67*[1]属性总表!$E$5</f>
-        <v>22312.5</v>
-      </c>
-      <c r="E67" s="1">
-        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
-        <v>1280</v>
-      </c>
-      <c r="F67" s="1">
-        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
-        <v>384</v>
-      </c>
-      <c r="G67" s="1">
-        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
-        <v>384</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="1">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1">
-        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
-        <v>21.5</v>
-      </c>
-      <c r="C68" s="1">
-        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
-        <v>12.91999999999997</v>
-      </c>
-      <c r="D68" s="1">
-        <f>B68*[1]属性总表!$E$5</f>
-        <v>22575</v>
-      </c>
-      <c r="E68" s="1">
-        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
-        <v>1292</v>
-      </c>
-      <c r="F68" s="1">
-        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
-        <v>388</v>
-      </c>
-      <c r="G68" s="1">
-        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
-        <v>388</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="1">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1">
-        <f t="shared" si="2"/>
-        <v>21.75</v>
-      </c>
-      <c r="C69" s="1">
-        <f t="shared" si="3"/>
-        <v>13.039999999999969</v>
-      </c>
-      <c r="D69" s="1">
-        <f>B69*[1]属性总表!$E$5</f>
-        <v>22837.5</v>
-      </c>
-      <c r="E69" s="1">
-        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
-        <v>1304</v>
-      </c>
-      <c r="F69" s="1">
-        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
-        <v>391</v>
-      </c>
-      <c r="G69" s="1">
-        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
-        <v>391</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="1">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1">
-        <f t="shared" si="2"/>
-        <v>22</v>
-      </c>
-      <c r="C70" s="1">
-        <f t="shared" si="3"/>
-        <v>13.159999999999968</v>
-      </c>
-      <c r="D70" s="1">
-        <f>B70*[1]属性总表!$E$5</f>
-        <v>23100</v>
-      </c>
-      <c r="E70" s="1">
-        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
-        <v>1316</v>
-      </c>
-      <c r="F70" s="1">
-        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
-        <v>395</v>
-      </c>
-      <c r="G70" s="1">
-        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
-        <v>395</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="1">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1">
-        <f t="shared" si="2"/>
-        <v>22.25</v>
-      </c>
-      <c r="C71" s="1">
-        <f t="shared" si="3"/>
-        <v>13.279999999999967</v>
-      </c>
-      <c r="D71" s="1">
-        <f>B71*[1]属性总表!$E$5</f>
-        <v>23362.5</v>
-      </c>
-      <c r="E71" s="1">
-        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
-        <v>1328</v>
-      </c>
-      <c r="F71" s="1">
-        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
-        <v>398</v>
-      </c>
-      <c r="G71" s="1">
-        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
-        <v>398</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="35" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:AM182"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -61057,7 +61034,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
   <dimension ref="B1:X50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -61400,7 +61377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
   <dimension ref="A3:J34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -61613,7 +61590,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
   <dimension ref="C1:R30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -62275,6 +62252,2077 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:H71"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="7" width="9" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1">
+        <f>B2*[1]属性总表!$E$5</f>
+        <v>5250</v>
+      </c>
+      <c r="E2" s="1">
+        <f>ROUND([1]等级属性!C2*[1]属性总表!$F$5,0)</f>
+        <v>500</v>
+      </c>
+      <c r="F2" s="1">
+        <f>ROUND(C2*[1]属性总表!$G$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="G2" s="1">
+        <f>ROUND(C2*[1]属性总表!$H$5,0)</f>
+        <v>150</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <f>B2+0.25</f>
+        <v>5.25</v>
+      </c>
+      <c r="C3" s="1">
+        <f>C2+0.12</f>
+        <v>5.12</v>
+      </c>
+      <c r="D3" s="1">
+        <f>B3*[1]属性总表!$E$5</f>
+        <v>5512.5</v>
+      </c>
+      <c r="E3" s="1">
+        <f>ROUND([1]等级属性!C3*[1]属性总表!$F$5,0)</f>
+        <v>512</v>
+      </c>
+      <c r="F3" s="1">
+        <f>ROUND(C3*[1]属性总表!$G$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="G3" s="1">
+        <f>ROUND(C3*[1]属性总表!$H$5,0)</f>
+        <v>154</v>
+      </c>
+      <c r="H3" s="1">
+        <f>D3-D2</f>
+        <v>262.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <f t="shared" ref="B4:B67" si="0">B3+0.25</f>
+        <v>5.5</v>
+      </c>
+      <c r="C4" s="1">
+        <f t="shared" ref="C4:C67" si="1">C3+0.12</f>
+        <v>5.24</v>
+      </c>
+      <c r="D4" s="1">
+        <f>B4*[1]属性总表!$E$5</f>
+        <v>5775</v>
+      </c>
+      <c r="E4" s="1">
+        <f>ROUND([1]等级属性!C4*[1]属性总表!$F$5,0)</f>
+        <v>524</v>
+      </c>
+      <c r="F4" s="1">
+        <f>ROUND(C4*[1]属性总表!$G$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="G4" s="1">
+        <f>ROUND(C4*[1]属性总表!$H$5,0)</f>
+        <v>157</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <f t="shared" si="0"/>
+        <v>5.75</v>
+      </c>
+      <c r="C5" s="1">
+        <f t="shared" si="1"/>
+        <v>5.36</v>
+      </c>
+      <c r="D5" s="1">
+        <f>B5*[1]属性总表!$E$5</f>
+        <v>6037.5</v>
+      </c>
+      <c r="E5" s="1">
+        <f>ROUND([1]等级属性!C5*[1]属性总表!$F$5,0)</f>
+        <v>536</v>
+      </c>
+      <c r="F5" s="1">
+        <f>ROUND(C5*[1]属性总表!$G$5,0)</f>
+        <v>161</v>
+      </c>
+      <c r="G5" s="1">
+        <f>ROUND(C5*[1]属性总表!$H$5,0)</f>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="C6" s="1">
+        <f t="shared" si="1"/>
+        <v>5.48</v>
+      </c>
+      <c r="D6" s="1">
+        <f>B6*[1]属性总表!$E$5</f>
+        <v>6300</v>
+      </c>
+      <c r="E6" s="1">
+        <f>ROUND([1]等级属性!C6*[1]属性总表!$F$5,0)</f>
+        <v>548</v>
+      </c>
+      <c r="F6" s="1">
+        <f>ROUND(C6*[1]属性总表!$G$5,0)</f>
+        <v>164</v>
+      </c>
+      <c r="G6" s="1">
+        <f>ROUND(C6*[1]属性总表!$H$5,0)</f>
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="C7" s="1">
+        <f t="shared" si="1"/>
+        <v>5.6000000000000005</v>
+      </c>
+      <c r="D7" s="1">
+        <f>B7*[1]属性总表!$E$5</f>
+        <v>6562.5</v>
+      </c>
+      <c r="E7" s="1">
+        <f>ROUND([1]等级属性!C7*[1]属性总表!$F$5,0)</f>
+        <v>560</v>
+      </c>
+      <c r="F7" s="1">
+        <f>ROUND(C7*[1]属性总表!$G$5,0)</f>
+        <v>168</v>
+      </c>
+      <c r="G7" s="1">
+        <f>ROUND(C7*[1]属性总表!$H$5,0)</f>
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <f t="shared" si="0"/>
+        <v>6.5</v>
+      </c>
+      <c r="C8" s="1">
+        <f t="shared" si="1"/>
+        <v>5.7200000000000006</v>
+      </c>
+      <c r="D8" s="1">
+        <f>B8*[1]属性总表!$E$5</f>
+        <v>6825</v>
+      </c>
+      <c r="E8" s="1">
+        <f>ROUND([1]等级属性!C8*[1]属性总表!$F$5,0)</f>
+        <v>572</v>
+      </c>
+      <c r="F8" s="1">
+        <f>ROUND(C8*[1]属性总表!$G$5,0)</f>
+        <v>172</v>
+      </c>
+      <c r="G8" s="1">
+        <f>ROUND(C8*[1]属性总表!$H$5,0)</f>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <f t="shared" si="0"/>
+        <v>6.75</v>
+      </c>
+      <c r="C9" s="1">
+        <f t="shared" si="1"/>
+        <v>5.8400000000000007</v>
+      </c>
+      <c r="D9" s="1">
+        <f>B9*[1]属性总表!$E$5</f>
+        <v>7087.5</v>
+      </c>
+      <c r="E9" s="1">
+        <f>ROUND([1]等级属性!C9*[1]属性总表!$F$5,0)</f>
+        <v>584</v>
+      </c>
+      <c r="F9" s="1">
+        <f>ROUND(C9*[1]属性总表!$G$5,0)</f>
+        <v>175</v>
+      </c>
+      <c r="G9" s="1">
+        <f>ROUND(C9*[1]属性总表!$H$5,0)</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="C10" s="1">
+        <f t="shared" si="1"/>
+        <v>5.9600000000000009</v>
+      </c>
+      <c r="D10" s="1">
+        <f>B10*[1]属性总表!$E$5</f>
+        <v>7350</v>
+      </c>
+      <c r="E10" s="1">
+        <f>ROUND([1]等级属性!C10*[1]属性总表!$F$5,0)</f>
+        <v>596</v>
+      </c>
+      <c r="F10" s="1">
+        <f>ROUND(C10*[1]属性总表!$G$5,0)</f>
+        <v>179</v>
+      </c>
+      <c r="G10" s="1">
+        <f>ROUND(C10*[1]属性总表!$H$5,0)</f>
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <f t="shared" si="0"/>
+        <v>7.25</v>
+      </c>
+      <c r="C11" s="1">
+        <f t="shared" si="1"/>
+        <v>6.080000000000001</v>
+      </c>
+      <c r="D11" s="1">
+        <f>B11*[1]属性总表!$E$5</f>
+        <v>7612.5</v>
+      </c>
+      <c r="E11" s="1">
+        <f>ROUND([1]等级属性!C11*[1]属性总表!$F$5,0)</f>
+        <v>608</v>
+      </c>
+      <c r="F11" s="1">
+        <f>ROUND(C11*[1]属性总表!$G$5,0)</f>
+        <v>182</v>
+      </c>
+      <c r="G11" s="1">
+        <f>ROUND(C11*[1]属性总表!$H$5,0)</f>
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1">
+        <f t="shared" si="0"/>
+        <v>7.5</v>
+      </c>
+      <c r="C12" s="1">
+        <f t="shared" si="1"/>
+        <v>6.2000000000000011</v>
+      </c>
+      <c r="D12" s="1">
+        <f>B12*[1]属性总表!$E$5</f>
+        <v>7875</v>
+      </c>
+      <c r="E12" s="1">
+        <f>ROUND([1]等级属性!C12*[1]属性总表!$F$5,0)</f>
+        <v>620</v>
+      </c>
+      <c r="F12" s="1">
+        <f>ROUND(C12*[1]属性总表!$G$5,0)</f>
+        <v>186</v>
+      </c>
+      <c r="G12" s="1">
+        <f>ROUND(C12*[1]属性总表!$H$5,0)</f>
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1">
+        <f t="shared" si="0"/>
+        <v>7.75</v>
+      </c>
+      <c r="C13" s="1">
+        <f t="shared" si="1"/>
+        <v>6.3200000000000012</v>
+      </c>
+      <c r="D13" s="1">
+        <f>B13*[1]属性总表!$E$5</f>
+        <v>8137.5</v>
+      </c>
+      <c r="E13" s="1">
+        <f>ROUND([1]等级属性!C13*[1]属性总表!$F$5,0)</f>
+        <v>632</v>
+      </c>
+      <c r="F13" s="1">
+        <f>ROUND(C13*[1]属性总表!$G$5,0)</f>
+        <v>190</v>
+      </c>
+      <c r="G13" s="1">
+        <f>ROUND(C13*[1]属性总表!$H$5,0)</f>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C14" s="1">
+        <f t="shared" si="1"/>
+        <v>6.4400000000000013</v>
+      </c>
+      <c r="D14" s="1">
+        <f>B14*[1]属性总表!$E$5</f>
+        <v>8400</v>
+      </c>
+      <c r="E14" s="1">
+        <f>ROUND([1]等级属性!C14*[1]属性总表!$F$5,0)</f>
+        <v>644</v>
+      </c>
+      <c r="F14" s="1">
+        <f>ROUND(C14*[1]属性总表!$G$5,0)</f>
+        <v>193</v>
+      </c>
+      <c r="G14" s="1">
+        <f>ROUND(C14*[1]属性总表!$H$5,0)</f>
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1">
+        <f t="shared" si="0"/>
+        <v>8.25</v>
+      </c>
+      <c r="C15" s="1">
+        <f t="shared" si="1"/>
+        <v>6.5600000000000014</v>
+      </c>
+      <c r="D15" s="1">
+        <f>B15*[1]属性总表!$E$5</f>
+        <v>8662.5</v>
+      </c>
+      <c r="E15" s="1">
+        <f>ROUND([1]等级属性!C15*[1]属性总表!$F$5,0)</f>
+        <v>656</v>
+      </c>
+      <c r="F15" s="1">
+        <f>ROUND(C15*[1]属性总表!$G$5,0)</f>
+        <v>197</v>
+      </c>
+      <c r="G15" s="1">
+        <f>ROUND(C15*[1]属性总表!$H$5,0)</f>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1">
+        <f t="shared" si="0"/>
+        <v>8.5</v>
+      </c>
+      <c r="C16" s="1">
+        <f t="shared" si="1"/>
+        <v>6.6800000000000015</v>
+      </c>
+      <c r="D16" s="1">
+        <f>B16*[1]属性总表!$E$5</f>
+        <v>8925</v>
+      </c>
+      <c r="E16" s="1">
+        <f>ROUND([1]等级属性!C16*[1]属性总表!$F$5,0)</f>
+        <v>668</v>
+      </c>
+      <c r="F16" s="1">
+        <f>ROUND(C16*[1]属性总表!$G$5,0)</f>
+        <v>200</v>
+      </c>
+      <c r="G16" s="1">
+        <f>ROUND(C16*[1]属性总表!$H$5,0)</f>
+        <v>200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1">
+        <f t="shared" si="0"/>
+        <v>8.75</v>
+      </c>
+      <c r="C17" s="1">
+        <f t="shared" si="1"/>
+        <v>6.8000000000000016</v>
+      </c>
+      <c r="D17" s="1">
+        <f>B17*[1]属性总表!$E$5</f>
+        <v>9187.5</v>
+      </c>
+      <c r="E17" s="1">
+        <f>ROUND([1]等级属性!C17*[1]属性总表!$F$5,0)</f>
+        <v>680</v>
+      </c>
+      <c r="F17" s="1">
+        <f>ROUND(C17*[1]属性总表!$G$5,0)</f>
+        <v>204</v>
+      </c>
+      <c r="G17" s="1">
+        <f>ROUND(C17*[1]属性总表!$H$5,0)</f>
+        <v>204</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="C18" s="1">
+        <f t="shared" si="1"/>
+        <v>6.9200000000000017</v>
+      </c>
+      <c r="D18" s="1">
+        <f>B18*[1]属性总表!$E$5</f>
+        <v>9450</v>
+      </c>
+      <c r="E18" s="1">
+        <f>ROUND([1]等级属性!C18*[1]属性总表!$F$5,0)</f>
+        <v>692</v>
+      </c>
+      <c r="F18" s="1">
+        <f>ROUND(C18*[1]属性总表!$G$5,0)</f>
+        <v>208</v>
+      </c>
+      <c r="G18" s="1">
+        <f>ROUND(C18*[1]属性总表!$H$5,0)</f>
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1">
+        <f t="shared" si="0"/>
+        <v>9.25</v>
+      </c>
+      <c r="C19" s="1">
+        <f t="shared" si="1"/>
+        <v>7.0400000000000018</v>
+      </c>
+      <c r="D19" s="1">
+        <f>B19*[1]属性总表!$E$5</f>
+        <v>9712.5</v>
+      </c>
+      <c r="E19" s="1">
+        <f>ROUND([1]等级属性!C19*[1]属性总表!$F$5,0)</f>
+        <v>704</v>
+      </c>
+      <c r="F19" s="1">
+        <f>ROUND(C19*[1]属性总表!$G$5,0)</f>
+        <v>211</v>
+      </c>
+      <c r="G19" s="1">
+        <f>ROUND(C19*[1]属性总表!$H$5,0)</f>
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1">
+        <f t="shared" si="0"/>
+        <v>9.5</v>
+      </c>
+      <c r="C20" s="1">
+        <f t="shared" si="1"/>
+        <v>7.1600000000000019</v>
+      </c>
+      <c r="D20" s="1">
+        <f>B20*[1]属性总表!$E$5</f>
+        <v>9975</v>
+      </c>
+      <c r="E20" s="1">
+        <f>ROUND([1]等级属性!C20*[1]属性总表!$F$5,0)</f>
+        <v>716</v>
+      </c>
+      <c r="F20" s="1">
+        <f>ROUND(C20*[1]属性总表!$G$5,0)</f>
+        <v>215</v>
+      </c>
+      <c r="G20" s="1">
+        <f>ROUND(C20*[1]属性总表!$H$5,0)</f>
+        <v>215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1">
+        <f t="shared" si="0"/>
+        <v>9.75</v>
+      </c>
+      <c r="C21" s="1">
+        <f t="shared" si="1"/>
+        <v>7.280000000000002</v>
+      </c>
+      <c r="D21" s="1">
+        <f>B21*[1]属性总表!$E$5</f>
+        <v>10237.5</v>
+      </c>
+      <c r="E21" s="1">
+        <f>ROUND([1]等级属性!C21*[1]属性总表!$F$5,0)</f>
+        <v>728</v>
+      </c>
+      <c r="F21" s="1">
+        <f>ROUND(C21*[1]属性总表!$G$5,0)</f>
+        <v>218</v>
+      </c>
+      <c r="G21" s="1">
+        <f>ROUND(C21*[1]属性总表!$H$5,0)</f>
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C22" s="1">
+        <f t="shared" si="1"/>
+        <v>7.4000000000000021</v>
+      </c>
+      <c r="D22" s="1">
+        <f>B22*[1]属性总表!$E$5</f>
+        <v>10500</v>
+      </c>
+      <c r="E22" s="1">
+        <f>ROUND([1]等级属性!C22*[1]属性总表!$F$5,0)</f>
+        <v>740</v>
+      </c>
+      <c r="F22" s="1">
+        <f>ROUND(C22*[1]属性总表!$G$5,0)</f>
+        <v>222</v>
+      </c>
+      <c r="G22" s="1">
+        <f>ROUND(C22*[1]属性总表!$H$5,0)</f>
+        <v>222</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1">
+        <f t="shared" si="0"/>
+        <v>10.25</v>
+      </c>
+      <c r="C23" s="1">
+        <f t="shared" si="1"/>
+        <v>7.5200000000000022</v>
+      </c>
+      <c r="D23" s="1">
+        <f>B23*[1]属性总表!$E$5</f>
+        <v>10762.5</v>
+      </c>
+      <c r="E23" s="1">
+        <f>ROUND([1]等级属性!C23*[1]属性总表!$F$5,0)</f>
+        <v>752</v>
+      </c>
+      <c r="F23" s="1">
+        <f>ROUND(C23*[1]属性总表!$G$5,0)</f>
+        <v>226</v>
+      </c>
+      <c r="G23" s="1">
+        <f>ROUND(C23*[1]属性总表!$H$5,0)</f>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1">
+        <f t="shared" si="0"/>
+        <v>10.5</v>
+      </c>
+      <c r="C24" s="1">
+        <f t="shared" si="1"/>
+        <v>7.6400000000000023</v>
+      </c>
+      <c r="D24" s="1">
+        <f>B24*[1]属性总表!$E$5</f>
+        <v>11025</v>
+      </c>
+      <c r="E24" s="1">
+        <f>ROUND([1]等级属性!C24*[1]属性总表!$F$5,0)</f>
+        <v>764</v>
+      </c>
+      <c r="F24" s="1">
+        <f>ROUND(C24*[1]属性总表!$G$5,0)</f>
+        <v>229</v>
+      </c>
+      <c r="G24" s="1">
+        <f>ROUND(C24*[1]属性总表!$H$5,0)</f>
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="1">
+        <f t="shared" si="0"/>
+        <v>10.75</v>
+      </c>
+      <c r="C25" s="1">
+        <f t="shared" si="1"/>
+        <v>7.7600000000000025</v>
+      </c>
+      <c r="D25" s="1">
+        <f>B25*[1]属性总表!$E$5</f>
+        <v>11287.5</v>
+      </c>
+      <c r="E25" s="1">
+        <f>ROUND([1]等级属性!C25*[1]属性总表!$F$5,0)</f>
+        <v>776</v>
+      </c>
+      <c r="F25" s="1">
+        <f>ROUND(C25*[1]属性总表!$G$5,0)</f>
+        <v>233</v>
+      </c>
+      <c r="G25" s="1">
+        <f>ROUND(C25*[1]属性总表!$H$5,0)</f>
+        <v>233</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="1">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="C26" s="1">
+        <f t="shared" si="1"/>
+        <v>7.8800000000000026</v>
+      </c>
+      <c r="D26" s="1">
+        <f>B26*[1]属性总表!$E$5</f>
+        <v>11550</v>
+      </c>
+      <c r="E26" s="1">
+        <f>ROUND([1]等级属性!C26*[1]属性总表!$F$5,0)</f>
+        <v>788</v>
+      </c>
+      <c r="F26" s="1">
+        <f>ROUND(C26*[1]属性总表!$G$5,0)</f>
+        <v>236</v>
+      </c>
+      <c r="G26" s="1">
+        <f>ROUND(C26*[1]属性总表!$H$5,0)</f>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="1">
+        <f t="shared" si="0"/>
+        <v>11.25</v>
+      </c>
+      <c r="C27" s="1">
+        <f t="shared" si="1"/>
+        <v>8.0000000000000018</v>
+      </c>
+      <c r="D27" s="1">
+        <f>B27*[1]属性总表!$E$5</f>
+        <v>11812.5</v>
+      </c>
+      <c r="E27" s="1">
+        <f>ROUND([1]等级属性!C27*[1]属性总表!$F$5,0)</f>
+        <v>800</v>
+      </c>
+      <c r="F27" s="1">
+        <f>ROUND(C27*[1]属性总表!$G$5,0)</f>
+        <v>240</v>
+      </c>
+      <c r="G27" s="1">
+        <f>ROUND(C27*[1]属性总表!$H$5,0)</f>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="1">
+        <f t="shared" si="0"/>
+        <v>11.5</v>
+      </c>
+      <c r="C28" s="1">
+        <f t="shared" si="1"/>
+        <v>8.120000000000001</v>
+      </c>
+      <c r="D28" s="1">
+        <f>B28*[1]属性总表!$E$5</f>
+        <v>12075</v>
+      </c>
+      <c r="E28" s="1">
+        <f>ROUND([1]等级属性!C28*[1]属性总表!$F$5,0)</f>
+        <v>812</v>
+      </c>
+      <c r="F28" s="1">
+        <f>ROUND(C28*[1]属性总表!$G$5,0)</f>
+        <v>244</v>
+      </c>
+      <c r="G28" s="1">
+        <f>ROUND(C28*[1]属性总表!$H$5,0)</f>
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="1">
+        <f t="shared" si="0"/>
+        <v>11.75</v>
+      </c>
+      <c r="C29" s="1">
+        <f t="shared" si="1"/>
+        <v>8.24</v>
+      </c>
+      <c r="D29" s="1">
+        <f>B29*[1]属性总表!$E$5</f>
+        <v>12337.5</v>
+      </c>
+      <c r="E29" s="1">
+        <f>ROUND([1]等级属性!C29*[1]属性总表!$F$5,0)</f>
+        <v>824</v>
+      </c>
+      <c r="F29" s="1">
+        <f>ROUND(C29*[1]属性总表!$G$5,0)</f>
+        <v>247</v>
+      </c>
+      <c r="G29" s="1">
+        <f>ROUND(C29*[1]属性总表!$H$5,0)</f>
+        <v>247</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="1">
+        <v>29</v>
+      </c>
+      <c r="B30" s="1">
+        <f t="shared" si="0"/>
+        <v>12</v>
+      </c>
+      <c r="C30" s="1">
+        <f t="shared" si="1"/>
+        <v>8.36</v>
+      </c>
+      <c r="D30" s="1">
+        <f>B30*[1]属性总表!$E$5</f>
+        <v>12600</v>
+      </c>
+      <c r="E30" s="1">
+        <f>ROUND([1]等级属性!C30*[1]属性总表!$F$5,0)</f>
+        <v>836</v>
+      </c>
+      <c r="F30" s="1">
+        <f>ROUND(C30*[1]属性总表!$G$5,0)</f>
+        <v>251</v>
+      </c>
+      <c r="G30" s="1">
+        <f>ROUND(C30*[1]属性总表!$H$5,0)</f>
+        <v>251</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="1">
+        <f t="shared" si="0"/>
+        <v>12.25</v>
+      </c>
+      <c r="C31" s="1">
+        <f t="shared" si="1"/>
+        <v>8.4799999999999986</v>
+      </c>
+      <c r="D31" s="1">
+        <f>B31*[1]属性总表!$E$5</f>
+        <v>12862.5</v>
+      </c>
+      <c r="E31" s="1">
+        <f>ROUND([1]等级属性!C31*[1]属性总表!$F$5,0)</f>
+        <v>848</v>
+      </c>
+      <c r="F31" s="1">
+        <f>ROUND(C31*[1]属性总表!$G$5,0)</f>
+        <v>254</v>
+      </c>
+      <c r="G31" s="1">
+        <f>ROUND(C31*[1]属性总表!$H$5,0)</f>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="1">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+      <c r="C32" s="1">
+        <f t="shared" si="1"/>
+        <v>8.5999999999999979</v>
+      </c>
+      <c r="D32" s="1">
+        <f>B32*[1]属性总表!$E$5</f>
+        <v>13125</v>
+      </c>
+      <c r="E32" s="1">
+        <f>ROUND([1]等级属性!C32*[1]属性总表!$F$5,0)</f>
+        <v>860</v>
+      </c>
+      <c r="F32" s="1">
+        <f>ROUND(C32*[1]属性总表!$G$5,0)</f>
+        <v>258</v>
+      </c>
+      <c r="G32" s="1">
+        <f>ROUND(C32*[1]属性总表!$H$5,0)</f>
+        <v>258</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="1">
+        <f t="shared" si="0"/>
+        <v>12.75</v>
+      </c>
+      <c r="C33" s="1">
+        <f t="shared" si="1"/>
+        <v>8.7199999999999971</v>
+      </c>
+      <c r="D33" s="1">
+        <f>B33*[1]属性总表!$E$5</f>
+        <v>13387.5</v>
+      </c>
+      <c r="E33" s="1">
+        <f>ROUND([1]等级属性!C33*[1]属性总表!$F$5,0)</f>
+        <v>872</v>
+      </c>
+      <c r="F33" s="1">
+        <f>ROUND(C33*[1]属性总表!$G$5,0)</f>
+        <v>262</v>
+      </c>
+      <c r="G33" s="1">
+        <f>ROUND(C33*[1]属性总表!$H$5,0)</f>
+        <v>262</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="1">
+        <f t="shared" si="0"/>
+        <v>13</v>
+      </c>
+      <c r="C34" s="1">
+        <f t="shared" si="1"/>
+        <v>8.8399999999999963</v>
+      </c>
+      <c r="D34" s="1">
+        <f>B34*[1]属性总表!$E$5</f>
+        <v>13650</v>
+      </c>
+      <c r="E34" s="1">
+        <f>ROUND([1]等级属性!C34*[1]属性总表!$F$5,0)</f>
+        <v>884</v>
+      </c>
+      <c r="F34" s="1">
+        <f>ROUND(C34*[1]属性总表!$G$5,0)</f>
+        <v>265</v>
+      </c>
+      <c r="G34" s="1">
+        <f>ROUND(C34*[1]属性总表!$H$5,0)</f>
+        <v>265</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="1">
+        <f t="shared" si="0"/>
+        <v>13.25</v>
+      </c>
+      <c r="C35" s="1">
+        <f t="shared" si="1"/>
+        <v>8.9599999999999955</v>
+      </c>
+      <c r="D35" s="1">
+        <f>B35*[1]属性总表!$E$5</f>
+        <v>13912.5</v>
+      </c>
+      <c r="E35" s="1">
+        <f>ROUND([1]等级属性!C35*[1]属性总表!$F$5,0)</f>
+        <v>896</v>
+      </c>
+      <c r="F35" s="1">
+        <f>ROUND(C35*[1]属性总表!$G$5,0)</f>
+        <v>269</v>
+      </c>
+      <c r="G35" s="1">
+        <f>ROUND(C35*[1]属性总表!$H$5,0)</f>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="1">
+        <f t="shared" si="0"/>
+        <v>13.5</v>
+      </c>
+      <c r="C36" s="1">
+        <f t="shared" si="1"/>
+        <v>9.0799999999999947</v>
+      </c>
+      <c r="D36" s="1">
+        <f>B36*[1]属性总表!$E$5</f>
+        <v>14175</v>
+      </c>
+      <c r="E36" s="1">
+        <f>ROUND([1]等级属性!C36*[1]属性总表!$F$5,0)</f>
+        <v>908</v>
+      </c>
+      <c r="F36" s="1">
+        <f>ROUND(C36*[1]属性总表!$G$5,0)</f>
+        <v>272</v>
+      </c>
+      <c r="G36" s="1">
+        <f>ROUND(C36*[1]属性总表!$H$5,0)</f>
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="1">
+        <f t="shared" si="0"/>
+        <v>13.75</v>
+      </c>
+      <c r="C37" s="1">
+        <f t="shared" si="1"/>
+        <v>9.199999999999994</v>
+      </c>
+      <c r="D37" s="1">
+        <f>B37*[1]属性总表!$E$5</f>
+        <v>14437.5</v>
+      </c>
+      <c r="E37" s="1">
+        <f>ROUND([1]等级属性!C37*[1]属性总表!$F$5,0)</f>
+        <v>920</v>
+      </c>
+      <c r="F37" s="1">
+        <f>ROUND(C37*[1]属性总表!$G$5,0)</f>
+        <v>276</v>
+      </c>
+      <c r="G37" s="1">
+        <f>ROUND(C37*[1]属性总表!$H$5,0)</f>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="1">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C38" s="1">
+        <f t="shared" si="1"/>
+        <v>9.3199999999999932</v>
+      </c>
+      <c r="D38" s="1">
+        <f>B38*[1]属性总表!$E$5</f>
+        <v>14700</v>
+      </c>
+      <c r="E38" s="1">
+        <f>ROUND([1]等级属性!C38*[1]属性总表!$F$5,0)</f>
+        <v>932</v>
+      </c>
+      <c r="F38" s="1">
+        <f>ROUND(C38*[1]属性总表!$G$5,0)</f>
+        <v>280</v>
+      </c>
+      <c r="G38" s="1">
+        <f>ROUND(C38*[1]属性总表!$H$5,0)</f>
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="1">
+        <f t="shared" si="0"/>
+        <v>14.25</v>
+      </c>
+      <c r="C39" s="1">
+        <f t="shared" si="1"/>
+        <v>9.4399999999999924</v>
+      </c>
+      <c r="D39" s="1">
+        <f>B39*[1]属性总表!$E$5</f>
+        <v>14962.5</v>
+      </c>
+      <c r="E39" s="1">
+        <f>ROUND([1]等级属性!C39*[1]属性总表!$F$5,0)</f>
+        <v>944</v>
+      </c>
+      <c r="F39" s="1">
+        <f>ROUND(C39*[1]属性总表!$G$5,0)</f>
+        <v>283</v>
+      </c>
+      <c r="G39" s="1">
+        <f>ROUND(C39*[1]属性总表!$H$5,0)</f>
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="1">
+        <f t="shared" si="0"/>
+        <v>14.5</v>
+      </c>
+      <c r="C40" s="1">
+        <f t="shared" si="1"/>
+        <v>9.5599999999999916</v>
+      </c>
+      <c r="D40" s="1">
+        <f>B40*[1]属性总表!$E$5</f>
+        <v>15225</v>
+      </c>
+      <c r="E40" s="1">
+        <f>ROUND([1]等级属性!C40*[1]属性总表!$F$5,0)</f>
+        <v>956</v>
+      </c>
+      <c r="F40" s="1">
+        <f>ROUND(C40*[1]属性总表!$G$5,0)</f>
+        <v>287</v>
+      </c>
+      <c r="G40" s="1">
+        <f>ROUND(C40*[1]属性总表!$H$5,0)</f>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="1">
+        <f t="shared" si="0"/>
+        <v>14.75</v>
+      </c>
+      <c r="C41" s="1">
+        <f t="shared" si="1"/>
+        <v>9.6799999999999908</v>
+      </c>
+      <c r="D41" s="1">
+        <f>B41*[1]属性总表!$E$5</f>
+        <v>15487.5</v>
+      </c>
+      <c r="E41" s="1">
+        <f>ROUND([1]等级属性!C41*[1]属性总表!$F$5,0)</f>
+        <v>968</v>
+      </c>
+      <c r="F41" s="1">
+        <f>ROUND(C41*[1]属性总表!$G$5,0)</f>
+        <v>290</v>
+      </c>
+      <c r="G41" s="1">
+        <f>ROUND(C41*[1]属性总表!$H$5,0)</f>
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="1">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="C42" s="1">
+        <f t="shared" si="1"/>
+        <v>9.7999999999999901</v>
+      </c>
+      <c r="D42" s="1">
+        <f>B42*[1]属性总表!$E$5</f>
+        <v>15750</v>
+      </c>
+      <c r="E42" s="1">
+        <f>ROUND([1]等级属性!C42*[1]属性总表!$F$5,0)</f>
+        <v>980</v>
+      </c>
+      <c r="F42" s="1">
+        <f>ROUND(C42*[1]属性总表!$G$5,0)</f>
+        <v>294</v>
+      </c>
+      <c r="G42" s="1">
+        <f>ROUND(C42*[1]属性总表!$H$5,0)</f>
+        <v>294</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="1">
+        <f t="shared" si="0"/>
+        <v>15.25</v>
+      </c>
+      <c r="C43" s="1">
+        <f t="shared" si="1"/>
+        <v>9.9199999999999893</v>
+      </c>
+      <c r="D43" s="1">
+        <f>B43*[1]属性总表!$E$5</f>
+        <v>16012.5</v>
+      </c>
+      <c r="E43" s="1">
+        <f>ROUND([1]等级属性!C43*[1]属性总表!$F$5,0)</f>
+        <v>992</v>
+      </c>
+      <c r="F43" s="1">
+        <f>ROUND(C43*[1]属性总表!$G$5,0)</f>
+        <v>298</v>
+      </c>
+      <c r="G43" s="1">
+        <f>ROUND(C43*[1]属性总表!$H$5,0)</f>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="1">
+        <f t="shared" si="0"/>
+        <v>15.5</v>
+      </c>
+      <c r="C44" s="1">
+        <f t="shared" si="1"/>
+        <v>10.039999999999988</v>
+      </c>
+      <c r="D44" s="1">
+        <f>B44*[1]属性总表!$E$5</f>
+        <v>16275</v>
+      </c>
+      <c r="E44" s="1">
+        <f>ROUND([1]等级属性!C44*[1]属性总表!$F$5,0)</f>
+        <v>1004</v>
+      </c>
+      <c r="F44" s="1">
+        <f>ROUND(C44*[1]属性总表!$G$5,0)</f>
+        <v>301</v>
+      </c>
+      <c r="G44" s="1">
+        <f>ROUND(C44*[1]属性总表!$H$5,0)</f>
+        <v>301</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="1">
+        <f t="shared" si="0"/>
+        <v>15.75</v>
+      </c>
+      <c r="C45" s="1">
+        <f t="shared" si="1"/>
+        <v>10.159999999999988</v>
+      </c>
+      <c r="D45" s="1">
+        <f>B45*[1]属性总表!$E$5</f>
+        <v>16537.5</v>
+      </c>
+      <c r="E45" s="1">
+        <f>ROUND([1]等级属性!C45*[1]属性总表!$F$5,0)</f>
+        <v>1016</v>
+      </c>
+      <c r="F45" s="1">
+        <f>ROUND(C45*[1]属性总表!$G$5,0)</f>
+        <v>305</v>
+      </c>
+      <c r="G45" s="1">
+        <f>ROUND(C45*[1]属性总表!$H$5,0)</f>
+        <v>305</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="1">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C46" s="1">
+        <f t="shared" si="1"/>
+        <v>10.279999999999987</v>
+      </c>
+      <c r="D46" s="1">
+        <f>B46*[1]属性总表!$E$5</f>
+        <v>16800</v>
+      </c>
+      <c r="E46" s="1">
+        <f>ROUND([1]等级属性!C46*[1]属性总表!$F$5,0)</f>
+        <v>1028</v>
+      </c>
+      <c r="F46" s="1">
+        <f>ROUND(C46*[1]属性总表!$G$5,0)</f>
+        <v>308</v>
+      </c>
+      <c r="G46" s="1">
+        <f>ROUND(C46*[1]属性总表!$H$5,0)</f>
+        <v>308</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="1">
+        <f t="shared" si="0"/>
+        <v>16.25</v>
+      </c>
+      <c r="C47" s="1">
+        <f t="shared" si="1"/>
+        <v>10.399999999999986</v>
+      </c>
+      <c r="D47" s="1">
+        <f>B47*[1]属性总表!$E$5</f>
+        <v>17062.5</v>
+      </c>
+      <c r="E47" s="1">
+        <f>ROUND([1]等级属性!C47*[1]属性总表!$F$5,0)</f>
+        <v>1040</v>
+      </c>
+      <c r="F47" s="1">
+        <f>ROUND(C47*[1]属性总表!$G$5,0)</f>
+        <v>312</v>
+      </c>
+      <c r="G47" s="1">
+        <f>ROUND(C47*[1]属性总表!$H$5,0)</f>
+        <v>312</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="1">
+        <f t="shared" si="0"/>
+        <v>16.5</v>
+      </c>
+      <c r="C48" s="1">
+        <f t="shared" si="1"/>
+        <v>10.519999999999985</v>
+      </c>
+      <c r="D48" s="1">
+        <f>B48*[1]属性总表!$E$5</f>
+        <v>17325</v>
+      </c>
+      <c r="E48" s="1">
+        <f>ROUND([1]等级属性!C48*[1]属性总表!$F$5,0)</f>
+        <v>1052</v>
+      </c>
+      <c r="F48" s="1">
+        <f>ROUND(C48*[1]属性总表!$G$5,0)</f>
+        <v>316</v>
+      </c>
+      <c r="G48" s="1">
+        <f>ROUND(C48*[1]属性总表!$H$5,0)</f>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="1">
+        <f t="shared" si="0"/>
+        <v>16.75</v>
+      </c>
+      <c r="C49" s="1">
+        <f t="shared" si="1"/>
+        <v>10.639999999999985</v>
+      </c>
+      <c r="D49" s="1">
+        <f>B49*[1]属性总表!$E$5</f>
+        <v>17587.5</v>
+      </c>
+      <c r="E49" s="1">
+        <f>ROUND([1]等级属性!C49*[1]属性总表!$F$5,0)</f>
+        <v>1064</v>
+      </c>
+      <c r="F49" s="1">
+        <f>ROUND(C49*[1]属性总表!$G$5,0)</f>
+        <v>319</v>
+      </c>
+      <c r="G49" s="1">
+        <f>ROUND(C49*[1]属性总表!$H$5,0)</f>
+        <v>319</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="1">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C50" s="1">
+        <f t="shared" si="1"/>
+        <v>10.759999999999984</v>
+      </c>
+      <c r="D50" s="1">
+        <f>B50*[1]属性总表!$E$5</f>
+        <v>17850</v>
+      </c>
+      <c r="E50" s="1">
+        <f>ROUND([1]等级属性!C50*[1]属性总表!$F$5,0)</f>
+        <v>1076</v>
+      </c>
+      <c r="F50" s="1">
+        <f>ROUND(C50*[1]属性总表!$G$5,0)</f>
+        <v>323</v>
+      </c>
+      <c r="G50" s="1">
+        <f>ROUND(C50*[1]属性总表!$H$5,0)</f>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="1">
+        <f t="shared" si="0"/>
+        <v>17.25</v>
+      </c>
+      <c r="C51" s="1">
+        <f t="shared" si="1"/>
+        <v>10.879999999999983</v>
+      </c>
+      <c r="D51" s="1">
+        <f>B51*[1]属性总表!$E$5</f>
+        <v>18112.5</v>
+      </c>
+      <c r="E51" s="1">
+        <f>ROUND([1]等级属性!C51*[1]属性总表!$F$5,0)</f>
+        <v>1088</v>
+      </c>
+      <c r="F51" s="1">
+        <f>ROUND(C51*[1]属性总表!$G$5,0)</f>
+        <v>326</v>
+      </c>
+      <c r="G51" s="1">
+        <f>ROUND(C51*[1]属性总表!$H$5,0)</f>
+        <v>326</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <f t="shared" si="0"/>
+        <v>17.5</v>
+      </c>
+      <c r="C52" s="1">
+        <f t="shared" si="1"/>
+        <v>10.999999999999982</v>
+      </c>
+      <c r="D52" s="1">
+        <f>B52*[1]属性总表!$E$5</f>
+        <v>18375</v>
+      </c>
+      <c r="E52" s="1">
+        <f>ROUND([1]等级属性!C52*[1]属性总表!$F$5,0)</f>
+        <v>1100</v>
+      </c>
+      <c r="F52" s="1">
+        <f>ROUND(C52*[1]属性总表!$G$5,0)</f>
+        <v>330</v>
+      </c>
+      <c r="G52" s="1">
+        <f>ROUND(C52*[1]属性总表!$H$5,0)</f>
+        <v>330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="1">
+        <f t="shared" si="0"/>
+        <v>17.75</v>
+      </c>
+      <c r="C53" s="1">
+        <f t="shared" si="1"/>
+        <v>11.119999999999981</v>
+      </c>
+      <c r="D53" s="1">
+        <f>B53*[1]属性总表!$E$5</f>
+        <v>18637.5</v>
+      </c>
+      <c r="E53" s="1">
+        <f>ROUND([1]等级属性!C53*[1]属性总表!$F$5,0)</f>
+        <v>1112</v>
+      </c>
+      <c r="F53" s="1">
+        <f>ROUND(C53*[1]属性总表!$G$5,0)</f>
+        <v>334</v>
+      </c>
+      <c r="G53" s="1">
+        <f>ROUND(C53*[1]属性总表!$H$5,0)</f>
+        <v>334</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C54" s="1">
+        <f t="shared" si="1"/>
+        <v>11.239999999999981</v>
+      </c>
+      <c r="D54" s="1">
+        <f>B54*[1]属性总表!$E$5</f>
+        <v>18900</v>
+      </c>
+      <c r="E54" s="1">
+        <f>ROUND([1]等级属性!C54*[1]属性总表!$F$5,0)</f>
+        <v>1124</v>
+      </c>
+      <c r="F54" s="1">
+        <f>ROUND(C54*[1]属性总表!$G$5,0)</f>
+        <v>337</v>
+      </c>
+      <c r="G54" s="1">
+        <f>ROUND(C54*[1]属性总表!$H$5,0)</f>
+        <v>337</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="1">
+        <f t="shared" si="0"/>
+        <v>18.25</v>
+      </c>
+      <c r="C55" s="1">
+        <f t="shared" si="1"/>
+        <v>11.35999999999998</v>
+      </c>
+      <c r="D55" s="1">
+        <f>B55*[1]属性总表!$E$5</f>
+        <v>19162.5</v>
+      </c>
+      <c r="E55" s="1">
+        <f>ROUND([1]等级属性!C55*[1]属性总表!$F$5,0)</f>
+        <v>1136</v>
+      </c>
+      <c r="F55" s="1">
+        <f>ROUND(C55*[1]属性总表!$G$5,0)</f>
+        <v>341</v>
+      </c>
+      <c r="G55" s="1">
+        <f>ROUND(C55*[1]属性总表!$H$5,0)</f>
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="1">
+        <f t="shared" si="0"/>
+        <v>18.5</v>
+      </c>
+      <c r="C56" s="1">
+        <f t="shared" si="1"/>
+        <v>11.479999999999979</v>
+      </c>
+      <c r="D56" s="1">
+        <f>B56*[1]属性总表!$E$5</f>
+        <v>19425</v>
+      </c>
+      <c r="E56" s="1">
+        <f>ROUND([1]等级属性!C56*[1]属性总表!$F$5,0)</f>
+        <v>1148</v>
+      </c>
+      <c r="F56" s="1">
+        <f>ROUND(C56*[1]属性总表!$G$5,0)</f>
+        <v>344</v>
+      </c>
+      <c r="G56" s="1">
+        <f>ROUND(C56*[1]属性总表!$H$5,0)</f>
+        <v>344</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="1">
+        <f t="shared" si="0"/>
+        <v>18.75</v>
+      </c>
+      <c r="C57" s="1">
+        <f t="shared" si="1"/>
+        <v>11.599999999999978</v>
+      </c>
+      <c r="D57" s="1">
+        <f>B57*[1]属性总表!$E$5</f>
+        <v>19687.5</v>
+      </c>
+      <c r="E57" s="1">
+        <f>ROUND([1]等级属性!C57*[1]属性总表!$F$5,0)</f>
+        <v>1160</v>
+      </c>
+      <c r="F57" s="1">
+        <f>ROUND(C57*[1]属性总表!$G$5,0)</f>
+        <v>348</v>
+      </c>
+      <c r="G57" s="1">
+        <f>ROUND(C57*[1]属性总表!$H$5,0)</f>
+        <v>348</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="1">
+        <f t="shared" si="0"/>
+        <v>19</v>
+      </c>
+      <c r="C58" s="1">
+        <f t="shared" si="1"/>
+        <v>11.719999999999978</v>
+      </c>
+      <c r="D58" s="1">
+        <f>B58*[1]属性总表!$E$5</f>
+        <v>19950</v>
+      </c>
+      <c r="E58" s="1">
+        <f>ROUND([1]等级属性!C58*[1]属性总表!$F$5,0)</f>
+        <v>1172</v>
+      </c>
+      <c r="F58" s="1">
+        <f>ROUND(C58*[1]属性总表!$G$5,0)</f>
+        <v>352</v>
+      </c>
+      <c r="G58" s="1">
+        <f>ROUND(C58*[1]属性总表!$H$5,0)</f>
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="1">
+        <f t="shared" si="0"/>
+        <v>19.25</v>
+      </c>
+      <c r="C59" s="1">
+        <f t="shared" si="1"/>
+        <v>11.839999999999977</v>
+      </c>
+      <c r="D59" s="1">
+        <f>B59*[1]属性总表!$E$5</f>
+        <v>20212.5</v>
+      </c>
+      <c r="E59" s="1">
+        <f>ROUND([1]等级属性!C59*[1]属性总表!$F$5,0)</f>
+        <v>1184</v>
+      </c>
+      <c r="F59" s="1">
+        <f>ROUND(C59*[1]属性总表!$G$5,0)</f>
+        <v>355</v>
+      </c>
+      <c r="G59" s="1">
+        <f>ROUND(C59*[1]属性总表!$H$5,0)</f>
+        <v>355</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="1">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="C60" s="1">
+        <f t="shared" si="1"/>
+        <v>11.959999999999976</v>
+      </c>
+      <c r="D60" s="1">
+        <f>B60*[1]属性总表!$E$5</f>
+        <v>20475</v>
+      </c>
+      <c r="E60" s="1">
+        <f>ROUND([1]等级属性!C60*[1]属性总表!$F$5,0)</f>
+        <v>1196</v>
+      </c>
+      <c r="F60" s="1">
+        <f>ROUND(C60*[1]属性总表!$G$5,0)</f>
+        <v>359</v>
+      </c>
+      <c r="G60" s="1">
+        <f>ROUND(C60*[1]属性总表!$H$5,0)</f>
+        <v>359</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="1">
+        <f t="shared" si="0"/>
+        <v>19.75</v>
+      </c>
+      <c r="C61" s="1">
+        <f t="shared" si="1"/>
+        <v>12.079999999999975</v>
+      </c>
+      <c r="D61" s="1">
+        <f>B61*[1]属性总表!$E$5</f>
+        <v>20737.5</v>
+      </c>
+      <c r="E61" s="1">
+        <f>ROUND([1]等级属性!C61*[1]属性总表!$F$5,0)</f>
+        <v>1208</v>
+      </c>
+      <c r="F61" s="1">
+        <f>ROUND(C61*[1]属性总表!$G$5,0)</f>
+        <v>362</v>
+      </c>
+      <c r="G61" s="1">
+        <f>ROUND(C61*[1]属性总表!$H$5,0)</f>
+        <v>362</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="1">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="C62" s="1">
+        <f t="shared" si="1"/>
+        <v>12.199999999999974</v>
+      </c>
+      <c r="D62" s="1">
+        <f>B62*[1]属性总表!$E$5</f>
+        <v>21000</v>
+      </c>
+      <c r="E62" s="1">
+        <f>ROUND([1]等级属性!C62*[1]属性总表!$F$5,0)</f>
+        <v>1220</v>
+      </c>
+      <c r="F62" s="1">
+        <f>ROUND(C62*[1]属性总表!$G$5,0)</f>
+        <v>366</v>
+      </c>
+      <c r="G62" s="1">
+        <f>ROUND(C62*[1]属性总表!$H$5,0)</f>
+        <v>366</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="1">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+      <c r="C63" s="1">
+        <f t="shared" si="1"/>
+        <v>12.319999999999974</v>
+      </c>
+      <c r="D63" s="1">
+        <f>B63*[1]属性总表!$E$5</f>
+        <v>21262.5</v>
+      </c>
+      <c r="E63" s="1">
+        <f>ROUND([1]等级属性!C63*[1]属性总表!$F$5,0)</f>
+        <v>1232</v>
+      </c>
+      <c r="F63" s="1">
+        <f>ROUND(C63*[1]属性总表!$G$5,0)</f>
+        <v>370</v>
+      </c>
+      <c r="G63" s="1">
+        <f>ROUND(C63*[1]属性总表!$H$5,0)</f>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="1">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+      <c r="C64" s="1">
+        <f t="shared" si="1"/>
+        <v>12.439999999999973</v>
+      </c>
+      <c r="D64" s="1">
+        <f>B64*[1]属性总表!$E$5</f>
+        <v>21525</v>
+      </c>
+      <c r="E64" s="1">
+        <f>ROUND([1]等级属性!C64*[1]属性总表!$F$5,0)</f>
+        <v>1244</v>
+      </c>
+      <c r="F64" s="1">
+        <f>ROUND(C64*[1]属性总表!$G$5,0)</f>
+        <v>373</v>
+      </c>
+      <c r="G64" s="1">
+        <f>ROUND(C64*[1]属性总表!$H$5,0)</f>
+        <v>373</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="1">
+        <f t="shared" si="0"/>
+        <v>20.75</v>
+      </c>
+      <c r="C65" s="1">
+        <f t="shared" si="1"/>
+        <v>12.559999999999972</v>
+      </c>
+      <c r="D65" s="1">
+        <f>B65*[1]属性总表!$E$5</f>
+        <v>21787.5</v>
+      </c>
+      <c r="E65" s="1">
+        <f>ROUND([1]等级属性!C65*[1]属性总表!$F$5,0)</f>
+        <v>1256</v>
+      </c>
+      <c r="F65" s="1">
+        <f>ROUND(C65*[1]属性总表!$G$5,0)</f>
+        <v>377</v>
+      </c>
+      <c r="G65" s="1">
+        <f>ROUND(C65*[1]属性总表!$H$5,0)</f>
+        <v>377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A66" s="1">
+        <v>65</v>
+      </c>
+      <c r="B66" s="1">
+        <f t="shared" si="0"/>
+        <v>21</v>
+      </c>
+      <c r="C66" s="1">
+        <f t="shared" si="1"/>
+        <v>12.679999999999971</v>
+      </c>
+      <c r="D66" s="1">
+        <f>B66*[1]属性总表!$E$5</f>
+        <v>22050</v>
+      </c>
+      <c r="E66" s="1">
+        <f>ROUND([1]等级属性!C66*[1]属性总表!$F$5,0)</f>
+        <v>1268</v>
+      </c>
+      <c r="F66" s="1">
+        <f>ROUND(C66*[1]属性总表!$G$5,0)</f>
+        <v>380</v>
+      </c>
+      <c r="G66" s="1">
+        <f>ROUND(C66*[1]属性总表!$H$5,0)</f>
+        <v>380</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A67" s="1">
+        <v>66</v>
+      </c>
+      <c r="B67" s="1">
+        <f t="shared" si="0"/>
+        <v>21.25</v>
+      </c>
+      <c r="C67" s="1">
+        <f t="shared" si="1"/>
+        <v>12.799999999999971</v>
+      </c>
+      <c r="D67" s="1">
+        <f>B67*[1]属性总表!$E$5</f>
+        <v>22312.5</v>
+      </c>
+      <c r="E67" s="1">
+        <f>ROUND([1]等级属性!C67*[1]属性总表!$F$5,0)</f>
+        <v>1280</v>
+      </c>
+      <c r="F67" s="1">
+        <f>ROUND(C67*[1]属性总表!$G$5,0)</f>
+        <v>384</v>
+      </c>
+      <c r="G67" s="1">
+        <f>ROUND(C67*[1]属性总表!$H$5,0)</f>
+        <v>384</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A68" s="1">
+        <v>67</v>
+      </c>
+      <c r="B68" s="1">
+        <f t="shared" ref="B68:B71" si="2">B67+0.25</f>
+        <v>21.5</v>
+      </c>
+      <c r="C68" s="1">
+        <f t="shared" ref="C68:C71" si="3">C67+0.12</f>
+        <v>12.91999999999997</v>
+      </c>
+      <c r="D68" s="1">
+        <f>B68*[1]属性总表!$E$5</f>
+        <v>22575</v>
+      </c>
+      <c r="E68" s="1">
+        <f>ROUND([1]等级属性!C68*[1]属性总表!$F$5,0)</f>
+        <v>1292</v>
+      </c>
+      <c r="F68" s="1">
+        <f>ROUND(C68*[1]属性总表!$G$5,0)</f>
+        <v>388</v>
+      </c>
+      <c r="G68" s="1">
+        <f>ROUND(C68*[1]属性总表!$H$5,0)</f>
+        <v>388</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A69" s="1">
+        <v>68</v>
+      </c>
+      <c r="B69" s="1">
+        <f t="shared" si="2"/>
+        <v>21.75</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" si="3"/>
+        <v>13.039999999999969</v>
+      </c>
+      <c r="D69" s="1">
+        <f>B69*[1]属性总表!$E$5</f>
+        <v>22837.5</v>
+      </c>
+      <c r="E69" s="1">
+        <f>ROUND([1]等级属性!C69*[1]属性总表!$F$5,0)</f>
+        <v>1304</v>
+      </c>
+      <c r="F69" s="1">
+        <f>ROUND(C69*[1]属性总表!$G$5,0)</f>
+        <v>391</v>
+      </c>
+      <c r="G69" s="1">
+        <f>ROUND(C69*[1]属性总表!$H$5,0)</f>
+        <v>391</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A70" s="1">
+        <v>69</v>
+      </c>
+      <c r="B70" s="1">
+        <f t="shared" si="2"/>
+        <v>22</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" si="3"/>
+        <v>13.159999999999968</v>
+      </c>
+      <c r="D70" s="1">
+        <f>B70*[1]属性总表!$E$5</f>
+        <v>23100</v>
+      </c>
+      <c r="E70" s="1">
+        <f>ROUND([1]等级属性!C70*[1]属性总表!$F$5,0)</f>
+        <v>1316</v>
+      </c>
+      <c r="F70" s="1">
+        <f>ROUND(C70*[1]属性总表!$G$5,0)</f>
+        <v>395</v>
+      </c>
+      <c r="G70" s="1">
+        <f>ROUND(C70*[1]属性总表!$H$5,0)</f>
+        <v>395</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="20.100000000000001" customHeight="1">
+      <c r="A71" s="1">
+        <v>70</v>
+      </c>
+      <c r="B71" s="1">
+        <f t="shared" si="2"/>
+        <v>22.25</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="3"/>
+        <v>13.279999999999967</v>
+      </c>
+      <c r="D71" s="1">
+        <f>B71*[1]属性总表!$E$5</f>
+        <v>23362.5</v>
+      </c>
+      <c r="E71" s="1">
+        <f>ROUND([1]等级属性!C71*[1]属性总表!$F$5,0)</f>
+        <v>1328</v>
+      </c>
+      <c r="F71" s="1">
+        <f>ROUND(C71*[1]属性总表!$G$5,0)</f>
+        <v>398</v>
+      </c>
+      <c r="G71" s="1">
+        <f>ROUND(C71*[1]属性总表!$H$5,0)</f>
+        <v>398</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="35" type="noConversion"/>
+  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:R30"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -62392,7 +64440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:CZ89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
@@ -66577,6 +68625,13 @@
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="CP23:CP25"/>
+    <mergeCell ref="CP26:CP28"/>
+    <mergeCell ref="CP8:CP10"/>
+    <mergeCell ref="CP11:CP13"/>
+    <mergeCell ref="CP14:CP16"/>
+    <mergeCell ref="CP17:CP19"/>
+    <mergeCell ref="CP20:CP22"/>
     <mergeCell ref="K18:K20"/>
     <mergeCell ref="K21:K23"/>
     <mergeCell ref="AX4:AX6"/>
@@ -66591,20 +68646,13 @@
     <mergeCell ref="K9:K11"/>
     <mergeCell ref="K12:K14"/>
     <mergeCell ref="K15:K17"/>
-    <mergeCell ref="CP23:CP25"/>
-    <mergeCell ref="CP26:CP28"/>
-    <mergeCell ref="CP8:CP10"/>
-    <mergeCell ref="CP11:CP13"/>
-    <mergeCell ref="CP14:CP16"/>
-    <mergeCell ref="CP17:CP19"/>
-    <mergeCell ref="CP20:CP22"/>
   </mergeCells>
   <phoneticPr fontId="35" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:BJ110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -72998,7 +75046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:U79"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -73995,7 +76043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B1:AY80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -77673,7 +79721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:AR285"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
@@ -83810,580 +85858,4 @@
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:R41"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="9" max="9" width="11.75" customWidth="1"/>
-    <col min="10" max="10" width="36.5" customWidth="1"/>
-    <col min="11" max="11" width="14.25" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="21.625" customWidth="1"/>
-    <col min="14" max="14" width="9" style="36"/>
-    <col min="16" max="16" width="23.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="N1" s="38"/>
-    </row>
-    <row r="2" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I2" s="1" t="s">
-        <v>1506</v>
-      </c>
-      <c r="N2" s="38"/>
-    </row>
-    <row r="3" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="H3" s="1" t="s">
-        <v>1507</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>1508</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>1509</v>
-      </c>
-      <c r="N3" s="38"/>
-    </row>
-    <row r="4" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I4" s="1">
-        <v>2</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>1510</v>
-      </c>
-      <c r="N4" s="38"/>
-    </row>
-    <row r="5" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I5" s="1">
-        <v>3</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>1511</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>1512</v>
-      </c>
-      <c r="N5" s="38"/>
-      <c r="P5" s="1">
-        <v>9</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>1513</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I6" s="1">
-        <v>4</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>1515</v>
-      </c>
-      <c r="N6" s="38"/>
-    </row>
-    <row r="7" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I7" s="1">
-        <v>5</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>1516</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>1514</v>
-      </c>
-      <c r="N7" s="38"/>
-    </row>
-    <row r="8" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I8" s="1">
-        <v>6</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>1517</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>1512</v>
-      </c>
-      <c r="N8" s="38"/>
-    </row>
-    <row r="9" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I9" s="1">
-        <v>7</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>1518</v>
-      </c>
-      <c r="K9" s="1">
-        <v>60000</v>
-      </c>
-      <c r="N9" s="38"/>
-    </row>
-    <row r="10" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I10" s="1">
-        <v>8</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>1519</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>1520</v>
-      </c>
-      <c r="N10" s="38"/>
-    </row>
-    <row r="11" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I11" s="1">
-        <v>10</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>1521</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>1522</v>
-      </c>
-      <c r="N11" s="38"/>
-    </row>
-    <row r="12" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="N12" s="38"/>
-    </row>
-    <row r="13" spans="1:18" s="5" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="J13" s="1" t="s">
-        <v>1523</v>
-      </c>
-      <c r="N13" s="38"/>
-      <c r="O13" s="1" t="s">
-        <v>1524</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="N14" s="7"/>
-    </row>
-    <row r="15" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="J15" s="1" t="s">
-        <v>1525</v>
-      </c>
-      <c r="N15" s="39" t="s">
-        <v>1526</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>1527</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="37" t="s">
-        <v>220</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>1528</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>1529</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>1530</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>1531</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>1532</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="37" t="s">
-        <v>312</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>1535</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>1536</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>1537</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>1538</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>1539</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="37" t="s">
-        <v>386</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>1540</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>1541</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>1542</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>1543</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>1544</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="C19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="N19" s="7" t="s">
-        <v>1546</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>1547</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>1548</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>1549</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>1550</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>1551</v>
-      </c>
-      <c r="N20" s="7"/>
-    </row>
-    <row r="21" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="37" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>1552</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>1553</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>1554</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>1555</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>1556</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="37" t="s">
-        <v>279</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>1559</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>1560</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>1561</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>1562</v>
-      </c>
-      <c r="N22" s="7"/>
-    </row>
-    <row r="23" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="J23" s="7"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="I24" s="1" t="s">
-        <v>1563</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>1564</v>
-      </c>
-      <c r="N24" s="7"/>
-    </row>
-    <row r="25" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="J25" s="7" t="s">
-        <v>1565</v>
-      </c>
-      <c r="N25" s="7"/>
-    </row>
-    <row r="26" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="J26" s="7"/>
-      <c r="N26" s="7"/>
-    </row>
-    <row r="27" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="N27" s="7"/>
-    </row>
-    <row r="28" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="1" t="s">
-        <v>1566</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>1264</v>
-      </c>
-      <c r="N28" s="7"/>
-      <c r="P28" s="7"/>
-    </row>
-    <row r="29" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="1" t="s">
-        <v>1567</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>1568</v>
-      </c>
-      <c r="G29" s="1">
-        <v>3</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>1569</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>1570</v>
-      </c>
-      <c r="N29" s="7"/>
-      <c r="O29" s="1">
-        <v>1</v>
-      </c>
-      <c r="P29" s="7" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="1" t="s">
-        <v>1572</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>1573</v>
-      </c>
-      <c r="G30" s="1">
-        <v>2</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>1574</v>
-      </c>
-      <c r="N30" s="7"/>
-      <c r="O30" s="1">
-        <v>2</v>
-      </c>
-      <c r="P30" s="7" t="s">
-        <v>1575</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>1576</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>1577</v>
-      </c>
-      <c r="G31" s="22">
-        <v>2</v>
-      </c>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1" t="s">
-        <v>1578</v>
-      </c>
-      <c r="N31" s="38"/>
-      <c r="O31" s="1">
-        <v>3</v>
-      </c>
-      <c r="P31" s="7" t="s">
-        <v>1579</v>
-      </c>
-      <c r="Q31" s="29"/>
-      <c r="R31" s="29"/>
-    </row>
-    <row r="32" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>1580</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1581</v>
-      </c>
-      <c r="G32" s="1">
-        <v>2</v>
-      </c>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="1">
-        <v>4</v>
-      </c>
-      <c r="P32" s="38"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-    </row>
-    <row r="33" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="B33" s="1">
-        <v>10</v>
-      </c>
-      <c r="G33" s="1">
-        <v>1</v>
-      </c>
-      <c r="I33">
-        <v>10</v>
-      </c>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="5"/>
-      <c r="P33" s="5"/>
-      <c r="Q33" s="5"/>
-      <c r="R33" s="5"/>
-    </row>
-    <row r="34" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="1" t="s">
-        <v>1583</v>
-      </c>
-      <c r="B34" s="1">
-        <v>10</v>
-      </c>
-      <c r="G34" s="1">
-        <v>1</v>
-      </c>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-    </row>
-    <row r="35" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="1" t="s">
-        <v>1584</v>
-      </c>
-      <c r="B35" s="1">
-        <v>10</v>
-      </c>
-      <c r="G35" s="1">
-        <v>1</v>
-      </c>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-    </row>
-    <row r="36" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>1585</v>
-      </c>
-      <c r="B36" s="1">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1">
-        <v>1</v>
-      </c>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="5"/>
-      <c r="R36" s="5"/>
-    </row>
-    <row r="37" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>1586</v>
-      </c>
-      <c r="B37" s="1">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1">
-        <v>1</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>1587</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>1588</v>
-      </c>
-      <c r="N37" s="38"/>
-      <c r="O37" s="1">
-        <v>1</v>
-      </c>
-      <c r="P37" s="5"/>
-      <c r="Q37" s="5"/>
-      <c r="R37" s="5"/>
-    </row>
-    <row r="38" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="L38" s="1"/>
-      <c r="M38" s="1" t="s">
-        <v>1589</v>
-      </c>
-      <c r="N38" s="38"/>
-      <c r="O38" s="1">
-        <v>2</v>
-      </c>
-      <c r="P38" s="5"/>
-      <c r="Q38" s="5"/>
-      <c r="R38" s="5"/>
-    </row>
-    <row r="39" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="5"/>
-      <c r="R39" s="5"/>
-    </row>
-    <row r="40" spans="1:18" ht="20.100000000000001" customHeight="1">
-      <c r="N40" s="38"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="5"/>
-      <c r="Q40" s="5"/>
-      <c r="R40" s="5"/>
-    </row>
-    <row r="41" spans="1:18">
-      <c r="N41" s="38"/>
-      <c r="O41" s="5"/>
-      <c r="P41" s="5"/>
-      <c r="Q41" s="5"/>
-      <c r="R41" s="5"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="35" type="noConversion"/>
-  <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>